--- a/giacenza_schede.xlsx
+++ b/giacenza_schede.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1729,7 +1729,11 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">

--- a/giacenza_schede.xlsx
+++ b/giacenza_schede.xlsx
@@ -4641,14 +4641,14 @@
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>36727</v>
+        <v>40237</v>
       </c>
       <c r="Z28" t="n">
-        <v>24334</v>
+        <v>26643</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-01 09:31:28</t>
+          <t>2026-10-08 08:09:34</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - FAUSTO LAI - Sardegna</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5113,7 +5113,7 @@
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - FAUSTO LAI - Sardegna</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5395,7 +5395,7 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr"/>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO GUASTI</t>
+          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6653,7 +6653,7 @@
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr"/>
@@ -8645,14 +8645,14 @@
       </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="n">
-        <v>39195</v>
+        <v>41542</v>
       </c>
       <c r="Z54" t="n">
-        <v>25935</v>
+        <v>27516</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-01 09:31:15</t>
+          <t>2026-10-08 08:09:23</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
@@ -9899,14 +9899,14 @@
       </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="n">
-        <v>41982</v>
+        <v>44564</v>
       </c>
       <c r="Z62" t="n">
-        <v>27351</v>
+        <v>28986</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-09-24 06:39:58</t>
+          <t>2026-10-08 07:36:14</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr"/>
@@ -18356,14 +18356,14 @@
       </c>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="n">
-        <v>49313</v>
+        <v>52696</v>
       </c>
       <c r="Z117" t="n">
-        <v>32312</v>
+        <v>34347</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-01 09:30:59</t>
+          <t>2026-10-08 08:09:13</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
@@ -28643,14 +28643,14 @@
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="n">
-        <v>68047</v>
+        <v>70079</v>
       </c>
       <c r="Z184" t="n">
-        <v>44027</v>
+        <v>45443</v>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-09-21 09:26:34</t>
+          <t>2026-10-08 08:55:42</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -29114,14 +29114,14 @@
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="n">
-        <v>66745</v>
+        <v>67833</v>
       </c>
       <c r="Z187" t="n">
-        <v>43258</v>
+        <v>43918</v>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2026-10-01 09:30:43</t>
+          <t>2026-10-08 08:08:59</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -37303,7 +37303,7 @@
       </c>
       <c r="AK241" t="inlineStr"/>
       <c r="AL241" t="n">
-        <v>2000</v>
+        <v>2071</v>
       </c>
       <c r="AM241" t="inlineStr"/>
       <c r="AN241" t="inlineStr"/>
@@ -38013,14 +38013,14 @@
       </c>
       <c r="X246" t="inlineStr"/>
       <c r="Y246" t="n">
-        <v>215161</v>
+        <v>225632</v>
       </c>
       <c r="Z246" t="n">
-        <v>139501</v>
+        <v>147197</v>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2026-07-31 08:32:25</t>
+          <t>2026-10-08 09:21:37</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr"/>
@@ -38315,14 +38315,14 @@
       </c>
       <c r="X248" t="inlineStr"/>
       <c r="Y248" t="n">
-        <v>119982</v>
+        <v>124392</v>
       </c>
       <c r="Z248" t="n">
-        <v>78003</v>
+        <v>81270</v>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2026-09-14 06:25:32</t>
+          <t>2026-10-08 08:31:20</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr"/>
@@ -41808,14 +41808,14 @@
       </c>
       <c r="X271" t="inlineStr"/>
       <c r="Y271" t="n">
-        <v>122024</v>
+        <v>126847</v>
       </c>
       <c r="Z271" t="n">
-        <v>79435</v>
+        <v>82486</v>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2026-09-21 09:28:00</t>
+          <t>2026-10-08 08:57:02</t>
         </is>
       </c>
       <c r="AB271" t="inlineStr"/>
@@ -51242,14 +51242,14 @@
       </c>
       <c r="X335" t="inlineStr"/>
       <c r="Y335" t="n">
-        <v>221489</v>
+        <v>224378</v>
       </c>
       <c r="Z335" t="n">
-        <v>144032</v>
+        <v>146340</v>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2026-09-24 06:41:44</t>
+          <t>2026-10-08 07:37:23</t>
         </is>
       </c>
       <c r="AB335" t="inlineStr"/>
@@ -61597,14 +61597,14 @@
       </c>
       <c r="X404" t="inlineStr"/>
       <c r="Y404" t="n">
-        <v>192181</v>
+        <v>193616</v>
       </c>
       <c r="Z404" t="n">
-        <v>125868</v>
+        <v>126635</v>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
-          <t>2026-09-21 09:28:10</t>
+          <t>2026-10-08 08:57:12</t>
         </is>
       </c>
       <c r="AB404" t="inlineStr"/>
@@ -66602,14 +66602,14 @@
       </c>
       <c r="X437" t="inlineStr"/>
       <c r="Y437" t="n">
-        <v>342242</v>
+        <v>345241</v>
       </c>
       <c r="Z437" t="n">
-        <v>223644</v>
+        <v>225600</v>
       </c>
       <c r="AA437" t="inlineStr">
         <is>
-          <t>2026-09-21 09:27:50</t>
+          <t>2026-10-08 08:56:51</t>
         </is>
       </c>
       <c r="AB437" t="inlineStr"/>
@@ -66751,14 +66751,14 @@
       </c>
       <c r="X438" t="inlineStr"/>
       <c r="Y438" t="n">
-        <v>216772</v>
+        <v>218504</v>
       </c>
       <c r="Z438" t="n">
-        <v>141416</v>
+        <v>142437</v>
       </c>
       <c r="AA438" t="inlineStr">
         <is>
-          <t>2026-09-24 06:41:18</t>
+          <t>2026-10-08 07:37:01</t>
         </is>
       </c>
       <c r="AB438" t="inlineStr"/>
@@ -66792,7 +66792,7 @@
       </c>
       <c r="AK438" t="inlineStr"/>
       <c r="AL438" t="n">
-        <v>900</v>
+        <v>1317</v>
       </c>
       <c r="AM438" t="inlineStr"/>
       <c r="AN438" t="inlineStr"/>
@@ -72947,14 +72947,14 @@
       </c>
       <c r="X479" t="inlineStr"/>
       <c r="Y479" t="n">
-        <v>263456</v>
+        <v>265388</v>
       </c>
       <c r="Z479" t="n">
-        <v>171211</v>
+        <v>172424</v>
       </c>
       <c r="AA479" t="inlineStr">
         <is>
-          <t>2026-09-28 07:19:43</t>
+          <t>2026-10-08 09:14:56</t>
         </is>
       </c>
       <c r="AB479" t="inlineStr"/>
@@ -77330,14 +77330,14 @@
       </c>
       <c r="X508" t="inlineStr"/>
       <c r="Y508" t="n">
-        <v>350609</v>
+        <v>352908</v>
       </c>
       <c r="Z508" t="n">
-        <v>228396</v>
+        <v>230032</v>
       </c>
       <c r="AA508" t="inlineStr">
         <is>
-          <t>2026-09-21 09:26:57</t>
+          <t>2026-10-08 08:56:13</t>
         </is>
       </c>
       <c r="AB508" t="inlineStr"/>
@@ -81520,14 +81520,14 @@
       </c>
       <c r="X536" t="inlineStr"/>
       <c r="Y536" t="n">
-        <v>459800</v>
+        <v>461697</v>
       </c>
       <c r="Z536" t="n">
-        <v>300059</v>
+        <v>301275</v>
       </c>
       <c r="AA536" t="inlineStr">
         <is>
-          <t>2026-09-21 09:26:49</t>
+          <t>2026-10-08 08:55:58</t>
         </is>
       </c>
       <c r="AB536" t="inlineStr"/>
@@ -84358,14 +84358,14 @@
       </c>
       <c r="X556" t="inlineStr"/>
       <c r="Y556" t="n">
-        <v>73021</v>
+        <v>76647</v>
       </c>
       <c r="Z556" t="n">
-        <v>47717</v>
+        <v>49729</v>
       </c>
       <c r="AA556" t="inlineStr">
         <is>
-          <t>2026-09-21 09:27:35</t>
+          <t>2026-10-08 08:56:27</t>
         </is>
       </c>
       <c r="AB556" t="inlineStr"/>
@@ -84642,14 +84642,14 @@
       </c>
       <c r="X558" t="inlineStr"/>
       <c r="Y558" t="n">
-        <v>101593</v>
+        <v>104263</v>
       </c>
       <c r="Z558" t="n">
-        <v>65978</v>
+        <v>67880</v>
       </c>
       <c r="AA558" t="inlineStr">
         <is>
-          <t>2026-09-21 09:26:20</t>
+          <t>2026-10-08 08:55:20</t>
         </is>
       </c>
       <c r="AB558" t="inlineStr"/>

--- a/giacenza_schede.xlsx
+++ b/giacenza_schede.xlsx
@@ -4804,14 +4804,14 @@
       </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>19586</v>
+        <v>23272</v>
       </c>
       <c r="Z29" t="n">
-        <v>12978</v>
+        <v>15098</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-24 08:12:29</t>
+          <t>2026-10-08 09:44:40</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -13629,14 +13629,14 @@
       </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="n">
-        <v>45373</v>
+        <v>47647</v>
       </c>
       <c r="Z86" t="n">
-        <v>29709</v>
+        <v>31370</v>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-09-17 08:59:51</t>
+          <t>2026-10-08 09:56:25</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr"/>
@@ -37262,14 +37262,14 @@
       </c>
       <c r="X241" t="inlineStr"/>
       <c r="Y241" t="n">
-        <v>132001</v>
+        <v>135528</v>
       </c>
       <c r="Z241" t="n">
-        <v>86306</v>
+        <v>88084</v>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2026-09-17 09:00:39</t>
+          <t>2026-10-08 09:47:22</t>
         </is>
       </c>
       <c r="AB241" t="inlineStr"/>
@@ -46482,14 +46482,14 @@
       </c>
       <c r="X303" t="inlineStr"/>
       <c r="Y303" t="n">
-        <v>174049</v>
+        <v>178739</v>
       </c>
       <c r="Z303" t="n">
-        <v>112920</v>
+        <v>116232</v>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>2026-09-17 09:01:05</t>
+          <t>2026-10-08 09:46:50</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr"/>

--- a/giacenza_schede.xlsx
+++ b/giacenza_schede.xlsx
@@ -40286,14 +40286,14 @@
       </c>
       <c r="X261" t="inlineStr"/>
       <c r="Y261" t="n">
-        <v>108744</v>
+        <v>109802</v>
       </c>
       <c r="Z261" t="n">
-        <v>70533</v>
+        <v>71165</v>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2026-09-29 08:20:01</t>
+          <t>2026-10-08 10:21:43</t>
         </is>
       </c>
       <c r="AB261" t="inlineStr"/>
@@ -45266,14 +45266,14 @@
       </c>
       <c r="X295" t="inlineStr"/>
       <c r="Y295" t="n">
-        <v>304276</v>
+        <v>306622</v>
       </c>
       <c r="Z295" t="n">
-        <v>197833</v>
+        <v>199779</v>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>2026-09-14 12:37:33</t>
+          <t>2026-10-08 10:22:13</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr"/>

--- a/giacenza_schede.xlsx
+++ b/giacenza_schede.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
+          <t>TABACCHERIA N. 10_NTS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1731,26 +1731,38 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>EA670043281S</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
       <c r="AQ9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1851,12 +1863,16 @@
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>9547</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
+        <v>6304</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:49:23</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
@@ -6550,7 +6566,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
+          <t>TABACCHERIA THE BLACK CROW DI PELLICANO' ROBERTO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6656,23 +6672,39 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
+      <c r="AF41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>E043013</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>EA570132577S</t>
+        </is>
+      </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
       <c r="AQ41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -9940,7 +9972,7 @@
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
@@ -10052,14 +10084,14 @@
       </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="n">
-        <v>39258</v>
+        <v>45243</v>
       </c>
       <c r="Z63" t="n">
-        <v>25383</v>
+        <v>29269</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-15 11:38:15</t>
+          <t>2026-10-08 11:28:18</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr"/>
@@ -10366,14 +10398,14 @@
       </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="n">
-        <v>33050</v>
+        <v>34566</v>
       </c>
       <c r="Z65" t="n">
-        <v>21528</v>
+        <v>22581</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-09-02 07:55:11</t>
+          <t>2026-10-09 07:48:36</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr"/>
@@ -11469,14 +11501,14 @@
       </c>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="n">
-        <v>58874</v>
+        <v>66405</v>
       </c>
       <c r="Z72" t="n">
-        <v>38250</v>
+        <v>43393</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:30</t>
+          <t>2026-10-08 12:35:12</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr"/>
@@ -13162,14 +13194,14 @@
       </c>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="n">
-        <v>39586</v>
+        <v>45654</v>
       </c>
       <c r="Z83" t="n">
-        <v>25814</v>
+        <v>29252</v>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-09-23 08:00:43</t>
+          <t>2026-10-08 09:51:52</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr"/>
@@ -16258,14 +16290,14 @@
       </c>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="n">
-        <v>93395</v>
+        <v>102188</v>
       </c>
       <c r="Z103" t="n">
-        <v>61261</v>
+        <v>67210</v>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-09-24 08:08:29</t>
+          <t>2026-10-09 09:59:04</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr"/>
@@ -18594,7 +18626,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>BAR ORNELLA</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -18697,42 +18729,26 @@
       <c r="AD119" t="inlineStr"/>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="AF119" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG119" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>E000878</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>EA230197328T</t>
-        </is>
-      </c>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
       <c r="AK119" t="inlineStr"/>
       <c r="AL119" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="AM119" t="inlineStr"/>
       <c r="AN119" t="inlineStr"/>
       <c r="AO119" t="inlineStr"/>
-      <c r="AP119" t="inlineStr">
-        <is>
-          <t>TV</t>
-        </is>
-      </c>
+      <c r="AP119" t="inlineStr"/>
       <c r="AQ119" t="inlineStr"/>
     </row>
     <row r="120">
@@ -18992,14 +19008,14 @@
       </c>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="n">
-        <v>13385</v>
+        <v>14170</v>
       </c>
       <c r="Z121" t="n">
-        <v>8657</v>
+        <v>9206</v>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-07-10 09:58:39</t>
+          <t>2026-10-09 08:21:55</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr"/>
@@ -19300,14 +19316,14 @@
       </c>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="n">
-        <v>17531</v>
+        <v>20100</v>
       </c>
       <c r="Z123" t="n">
-        <v>11548</v>
+        <v>13127</v>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-09-14 06:27:10</t>
+          <t>2026-10-08 12:28:58</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
@@ -20794,14 +20810,14 @@
       </c>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="n">
-        <v>61427</v>
+        <v>72537</v>
       </c>
       <c r="Z133" t="n">
-        <v>39871</v>
+        <v>47225</v>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-08-28 07:38:45</t>
+          <t>2026-10-09 07:16:15</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr"/>
@@ -22173,14 +22189,14 @@
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="n">
-        <v>31662</v>
+        <v>32850</v>
       </c>
       <c r="Z142" t="n">
-        <v>20675</v>
+        <v>21342</v>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-09-23 15:08:01</t>
+          <t>2026-10-09 05:38:17</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -22328,14 +22344,14 @@
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="n">
-        <v>59528</v>
+        <v>69972</v>
       </c>
       <c r="Z143" t="n">
-        <v>38826</v>
+        <v>46131</v>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-07-30 08:04:46</t>
+          <t>2026-10-09 06:27:45</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -22483,14 +22499,14 @@
       </c>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="n">
-        <v>54232</v>
+        <v>60249</v>
       </c>
       <c r="Z144" t="n">
-        <v>35182</v>
+        <v>39331</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-08-28 07:42:33</t>
+          <t>2026-10-09 07:18:42</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -22634,14 +22650,14 @@
       </c>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="n">
-        <v>80919</v>
+        <v>102371</v>
       </c>
       <c r="Z145" t="n">
-        <v>52422</v>
+        <v>66826</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-07-30 08:06:39</t>
+          <t>2026-10-09 06:28:09</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -22936,14 +22952,14 @@
       </c>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="n">
-        <v>50007</v>
+        <v>53691</v>
       </c>
       <c r="Z147" t="n">
-        <v>32707</v>
+        <v>35321</v>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-08-28 07:42:55</t>
+          <t>2026-10-09 07:19:04</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -23087,14 +23103,14 @@
       </c>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="n">
-        <v>26084</v>
+        <v>27177</v>
       </c>
       <c r="Z148" t="n">
-        <v>17296</v>
+        <v>17900</v>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-09-18 07:37:41</t>
+          <t>2026-10-09 06:58:27</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -23691,14 +23707,14 @@
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="n">
-        <v>56602</v>
+        <v>60331</v>
       </c>
       <c r="Z152" t="n">
-        <v>37106</v>
+        <v>39337</v>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-08-28 07:39:01</t>
+          <t>2026-10-09 07:18:16</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -23846,14 +23862,14 @@
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="n">
-        <v>32190</v>
+        <v>33661</v>
       </c>
       <c r="Z153" t="n">
-        <v>21113</v>
+        <v>21871</v>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-09-23 15:07:37</t>
+          <t>2026-10-09 05:36:59</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -24156,14 +24172,14 @@
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="n">
-        <v>35817</v>
+        <v>38256</v>
       </c>
       <c r="Z155" t="n">
-        <v>23286</v>
+        <v>25039</v>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-09-14 09:41:25</t>
+          <t>2026-10-08 12:30:17</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -24780,14 +24796,14 @@
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="n">
-        <v>27355</v>
+        <v>28258</v>
       </c>
       <c r="Z159" t="n">
-        <v>18004</v>
+        <v>18514</v>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-09-18 07:37:20</t>
+          <t>2026-10-09 06:56:47</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -25722,14 +25738,14 @@
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="n">
-        <v>99400</v>
+        <v>100753</v>
       </c>
       <c r="Z165" t="n">
-        <v>64466</v>
+        <v>65362</v>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-09-23 08:43:25</t>
+          <t>2026-10-08 09:52:38</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -26779,14 +26795,14 @@
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="n">
-        <v>43728</v>
+        <v>45140</v>
       </c>
       <c r="Z172" t="n">
-        <v>27606</v>
+        <v>28594</v>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-09-02 07:54:59</t>
+          <t>2026-10-09 07:48:06</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -27947,7 +27963,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
+          <t>BAR EDEN</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -28050,26 +28066,38 @@
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr"/>
-      <c r="AG180" t="inlineStr"/>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AF180" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>0</v>
+      </c>
       <c r="AH180" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="AI180" t="inlineStr"/>
-      <c r="AJ180" t="inlineStr"/>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>EA580114981R</t>
+        </is>
+      </c>
       <c r="AK180" t="inlineStr"/>
       <c r="AL180" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AM180" t="inlineStr"/>
       <c r="AN180" t="inlineStr"/>
       <c r="AO180" t="inlineStr"/>
-      <c r="AP180" t="inlineStr"/>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
       <c r="AQ180" t="inlineStr"/>
     </row>
     <row r="181">
@@ -29916,7 +29944,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
+          <t>BAR ORNELLA</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -30019,26 +30047,42 @@
       <c r="AD193" t="inlineStr"/>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr"/>
-      <c r="AG193" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AF193" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>0</v>
+      </c>
       <c r="AH193" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI193" t="inlineStr"/>
-      <c r="AJ193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>E000878</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>EA230197328T</t>
+        </is>
+      </c>
       <c r="AK193" t="inlineStr"/>
       <c r="AL193" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AM193" t="inlineStr"/>
       <c r="AN193" t="inlineStr"/>
       <c r="AO193" t="inlineStr"/>
-      <c r="AP193" t="inlineStr"/>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
       <c r="AQ193" t="inlineStr"/>
     </row>
     <row r="194">
@@ -31399,14 +31443,14 @@
       </c>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="n">
-        <v>89499</v>
+        <v>93886</v>
       </c>
       <c r="Z202" t="n">
-        <v>58197</v>
+        <v>61291</v>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2026-09-16 14:08:04</t>
+          <t>2026-10-08 12:21:45</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -33147,7 +33191,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
+          <t>SALA SLOT VLT</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -33242,18 +33286,30 @@
       <c r="AD214" t="inlineStr"/>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr"/>
-      <c r="AG214" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AF214" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>0</v>
+      </c>
       <c r="AH214" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI214" t="inlineStr"/>
-      <c r="AJ214" t="inlineStr"/>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>E048071</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>EA600145288K</t>
+        </is>
+      </c>
       <c r="AK214" t="inlineStr"/>
       <c r="AL214" t="n">
         <v>0</v>
@@ -33261,7 +33317,11 @@
       <c r="AM214" t="inlineStr"/>
       <c r="AN214" t="inlineStr"/>
       <c r="AO214" t="inlineStr"/>
-      <c r="AP214" t="inlineStr"/>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
       <c r="AQ214" t="inlineStr"/>
     </row>
     <row r="215">
@@ -34717,14 +34777,14 @@
       </c>
       <c r="X224" t="inlineStr"/>
       <c r="Y224" t="n">
-        <v>114882</v>
+        <v>116223</v>
       </c>
       <c r="Z224" t="n">
-        <v>74886</v>
+        <v>75548</v>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15:39</t>
+          <t>2026-10-08 09:52:50</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr"/>
@@ -35023,14 +35083,14 @@
       </c>
       <c r="X226" t="inlineStr"/>
       <c r="Y226" t="n">
-        <v>89098</v>
+        <v>91304</v>
       </c>
       <c r="Z226" t="n">
-        <v>58038</v>
+        <v>59429</v>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2026-07-28 12:15:34</t>
+          <t>2026-10-08 11:28:31</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr"/>
@@ -36499,14 +36559,14 @@
       </c>
       <c r="X236" t="inlineStr"/>
       <c r="Y236" t="n">
-        <v>134676</v>
+        <v>140232</v>
       </c>
       <c r="Z236" t="n">
-        <v>87961</v>
+        <v>91119</v>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2026-09-24 08:06:58</t>
+          <t>2026-10-09 09:57:39</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr"/>
@@ -37937,7 +37997,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>TABACCHERIA N. 10</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -38032,42 +38092,26 @@
       <c r="AD246" t="inlineStr"/>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="AF246" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG246" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr"/>
+      <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>E048752</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>EA670043281S</t>
-        </is>
-      </c>
+      <c r="AI246" t="inlineStr"/>
+      <c r="AJ246" t="inlineStr"/>
       <c r="AK246" t="inlineStr"/>
       <c r="AL246" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AM246" t="inlineStr"/>
       <c r="AN246" t="inlineStr"/>
       <c r="AO246" t="inlineStr"/>
-      <c r="AP246" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
+      <c r="AP246" t="inlineStr"/>
       <c r="AQ246" t="inlineStr"/>
     </row>
     <row r="247">
@@ -39984,14 +40028,14 @@
       </c>
       <c r="X259" t="inlineStr"/>
       <c r="Y259" t="n">
-        <v>149199</v>
+        <v>152624</v>
       </c>
       <c r="Z259" t="n">
-        <v>97009</v>
+        <v>99310</v>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:46</t>
+          <t>2026-10-08 12:32:36</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr"/>
@@ -40180,7 +40224,7 @@
       </c>
       <c r="AK260" t="inlineStr"/>
       <c r="AL260" t="n">
-        <v>2027</v>
+        <v>1202</v>
       </c>
       <c r="AM260" t="inlineStr"/>
       <c r="AN260" t="inlineStr"/>
@@ -40210,7 +40254,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>TABACCHERIA THE BLACK CROW DI PELLICANO' ROBERTO</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -40309,42 +40353,26 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="AF261" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG261" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr"/>
+      <c r="AG261" t="inlineStr"/>
       <c r="AH261" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>E043013</t>
-        </is>
-      </c>
-      <c r="AJ261" t="inlineStr">
-        <is>
-          <t>EA570132577S</t>
-        </is>
-      </c>
+      <c r="AI261" t="inlineStr"/>
+      <c r="AJ261" t="inlineStr"/>
       <c r="AK261" t="inlineStr"/>
       <c r="AL261" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="AM261" t="inlineStr"/>
       <c r="AN261" t="inlineStr"/>
       <c r="AO261" t="inlineStr"/>
-      <c r="AP261" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+      <c r="AP261" t="inlineStr"/>
       <c r="AQ261" t="inlineStr"/>
     </row>
     <row r="262">
@@ -47229,14 +47257,14 @@
       </c>
       <c r="X308" t="inlineStr"/>
       <c r="Y308" t="n">
-        <v>285713</v>
+        <v>289080</v>
       </c>
       <c r="Z308" t="n">
-        <v>185745</v>
+        <v>187898</v>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
-          <t>2026-09-10 08:47:21</t>
+          <t>2026-10-09 08:21:40</t>
         </is>
       </c>
       <c r="AB308" t="inlineStr"/>
@@ -47270,7 +47298,7 @@
       </c>
       <c r="AK308" t="inlineStr"/>
       <c r="AL308" t="n">
-        <v>1284</v>
+        <v>300</v>
       </c>
       <c r="AM308" t="inlineStr"/>
       <c r="AN308" t="inlineStr"/>
@@ -48214,7 +48242,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>SALA SLOT VLT</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -48309,30 +48337,18 @@
       <c r="AD315" t="inlineStr"/>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="AF315" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG315" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr"/>
+      <c r="AG315" t="inlineStr"/>
       <c r="AH315" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>E048071</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>EA600145288K</t>
-        </is>
-      </c>
+      <c r="AI315" t="inlineStr"/>
+      <c r="AJ315" t="inlineStr"/>
       <c r="AK315" t="inlineStr"/>
       <c r="AL315" t="n">
         <v>0</v>
@@ -48340,11 +48356,7 @@
       <c r="AM315" t="inlineStr"/>
       <c r="AN315" t="inlineStr"/>
       <c r="AO315" t="inlineStr"/>
-      <c r="AP315" t="inlineStr">
-        <is>
-          <t>SO</t>
-        </is>
-      </c>
+      <c r="AP315" t="inlineStr"/>
       <c r="AQ315" t="inlineStr"/>
     </row>
     <row r="316">
@@ -49573,14 +49585,14 @@
       </c>
       <c r="X324" t="inlineStr"/>
       <c r="Y324" t="n">
-        <v>328312</v>
+        <v>332987</v>
       </c>
       <c r="Z324" t="n">
-        <v>214446</v>
+        <v>217219</v>
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>2026-09-16 14:07:13</t>
+          <t>2026-10-08 12:20:49</t>
         </is>
       </c>
       <c r="AB324" t="inlineStr"/>
@@ -54615,7 +54627,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO GUASTI</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -54710,7 +54722,7 @@
       <c r="AD358" t="inlineStr"/>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr"/>
@@ -55128,14 +55140,14 @@
       </c>
       <c r="X361" t="inlineStr"/>
       <c r="Y361" t="n">
-        <v>383843</v>
+        <v>390268</v>
       </c>
       <c r="Z361" t="n">
-        <v>249846</v>
+        <v>254033</v>
       </c>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>2026-09-24 08:08:17</t>
+          <t>2026-10-09 09:55:26</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr"/>
@@ -57103,14 +57115,14 @@
       </c>
       <c r="X374" t="inlineStr"/>
       <c r="Y374" t="n">
-        <v>197583</v>
+        <v>201430</v>
       </c>
       <c r="Z374" t="n">
-        <v>128544</v>
+        <v>131347</v>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
-          <t>2026-09-23 12:25:48</t>
+          <t>2026-10-08 13:48:06</t>
         </is>
       </c>
       <c r="AB374" t="inlineStr"/>
@@ -57148,7 +57160,7 @@
       </c>
       <c r="AK374" t="inlineStr"/>
       <c r="AL374" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AM374" t="inlineStr"/>
       <c r="AN374" t="inlineStr"/>
@@ -62048,14 +62060,14 @@
       </c>
       <c r="X407" t="inlineStr"/>
       <c r="Y407" t="n">
-        <v>357809</v>
+        <v>363763</v>
       </c>
       <c r="Z407" t="n">
-        <v>233034</v>
+        <v>236920</v>
       </c>
       <c r="AA407" t="inlineStr">
         <is>
-          <t>2026-09-24 08:07:14</t>
+          <t>2026-10-09 10:01:25</t>
         </is>
       </c>
       <c r="AB407" t="inlineStr"/>
@@ -64333,14 +64345,14 @@
       </c>
       <c r="X422" t="inlineStr"/>
       <c r="Y422" t="n">
-        <v>289050</v>
+        <v>296218</v>
       </c>
       <c r="Z422" t="n">
-        <v>188040</v>
+        <v>192722</v>
       </c>
       <c r="AA422" t="inlineStr">
         <is>
-          <t>2026-09-16 14:06:03</t>
+          <t>2026-10-08 12:18:02</t>
         </is>
       </c>
       <c r="AB422" t="inlineStr"/>
@@ -65553,14 +65565,14 @@
       </c>
       <c r="X430" t="inlineStr"/>
       <c r="Y430" t="n">
-        <v>648480</v>
+        <v>649613</v>
       </c>
       <c r="Z430" t="n">
-        <v>423223</v>
+        <v>423882</v>
       </c>
       <c r="AA430" t="inlineStr">
         <is>
-          <t>2026-09-23 08:03:27</t>
+          <t>2026-10-08 09:52:12</t>
         </is>
       </c>
       <c r="AB430" t="inlineStr"/>
@@ -66006,14 +66018,14 @@
       </c>
       <c r="X433" t="inlineStr"/>
       <c r="Y433" t="n">
-        <v>248124</v>
+        <v>252118</v>
       </c>
       <c r="Z433" t="n">
-        <v>161619</v>
+        <v>164303</v>
       </c>
       <c r="AA433" t="inlineStr">
         <is>
-          <t>2026-09-16 14:07:26</t>
+          <t>2026-10-08 12:21:14</t>
         </is>
       </c>
       <c r="AB433" t="inlineStr"/>
@@ -66675,7 +66687,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>BAR EDEN</t>
+          <t>WINGAMING SRL - DEPOSITO GUASTI</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -66770,38 +66782,26 @@
       <c r="AD438" t="inlineStr"/>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="AF438" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG438" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AF438" t="inlineStr"/>
+      <c r="AG438" t="inlineStr"/>
       <c r="AH438" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="AI438" t="inlineStr"/>
-      <c r="AJ438" t="inlineStr">
-        <is>
-          <t>EA580114981R</t>
-        </is>
-      </c>
+      <c r="AJ438" t="inlineStr"/>
       <c r="AK438" t="inlineStr"/>
       <c r="AL438" t="n">
-        <v>1317</v>
+        <v>0</v>
       </c>
       <c r="AM438" t="inlineStr"/>
       <c r="AN438" t="inlineStr"/>
       <c r="AO438" t="inlineStr"/>
-      <c r="AP438" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
+      <c r="AP438" t="inlineStr"/>
       <c r="AQ438" t="inlineStr"/>
     </row>
     <row r="439">
@@ -68095,14 +68095,14 @@
       </c>
       <c r="X447" t="inlineStr"/>
       <c r="Y447" t="n">
-        <v>594706</v>
+        <v>598663</v>
       </c>
       <c r="Z447" t="n">
-        <v>387536</v>
+        <v>390513</v>
       </c>
       <c r="AA447" t="inlineStr">
         <is>
-          <t>2026-09-24 08:08:49</t>
+          <t>2026-10-09 09:58:22</t>
         </is>
       </c>
       <c r="AB447" t="inlineStr"/>
@@ -70070,14 +70070,14 @@
       </c>
       <c r="X460" t="inlineStr"/>
       <c r="Y460" t="n">
-        <v>458320</v>
+        <v>463270</v>
       </c>
       <c r="Z460" t="n">
-        <v>299198</v>
+        <v>302382</v>
       </c>
       <c r="AA460" t="inlineStr">
         <is>
-          <t>2026-09-15 11:36:50</t>
+          <t>2026-10-08 11:31:24</t>
         </is>
       </c>
       <c r="AB460" t="inlineStr"/>
@@ -71723,14 +71723,14 @@
       </c>
       <c r="X471" t="inlineStr"/>
       <c r="Y471" t="n">
-        <v>456607</v>
+        <v>463457</v>
       </c>
       <c r="Z471" t="n">
-        <v>298041</v>
+        <v>302340</v>
       </c>
       <c r="AA471" t="inlineStr">
         <is>
-          <t>2026-09-15 11:36:15</t>
+          <t>2026-10-08 11:30:55</t>
         </is>
       </c>
       <c r="AB471" t="inlineStr"/>
@@ -72996,7 +72996,7 @@
       </c>
       <c r="AK479" t="inlineStr"/>
       <c r="AL479" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AM479" t="inlineStr"/>
       <c r="AN479" t="inlineStr"/>
@@ -73102,14 +73102,14 @@
       </c>
       <c r="X480" t="inlineStr"/>
       <c r="Y480" t="n">
-        <v>427874</v>
+        <v>432530</v>
       </c>
       <c r="Z480" t="n">
-        <v>279364</v>
+        <v>282497</v>
       </c>
       <c r="AA480" t="inlineStr">
         <is>
-          <t>2026-09-23 12:26:11</t>
+          <t>2026-10-08 13:49:40</t>
         </is>
       </c>
       <c r="AB480" t="inlineStr"/>
@@ -74016,14 +74016,14 @@
       </c>
       <c r="X486" t="inlineStr"/>
       <c r="Y486" t="n">
-        <v>275439</v>
+        <v>277751</v>
       </c>
       <c r="Z486" t="n">
-        <v>179592</v>
+        <v>181384</v>
       </c>
       <c r="AA486" t="inlineStr">
         <is>
-          <t>2026-09-16 14:08:28</t>
+          <t>2026-10-08 12:21:31</t>
         </is>
       </c>
       <c r="AB486" t="inlineStr"/>
@@ -77175,14 +77175,14 @@
       </c>
       <c r="X507" t="inlineStr"/>
       <c r="Y507" t="n">
-        <v>288251</v>
+        <v>291656</v>
       </c>
       <c r="Z507" t="n">
-        <v>187809</v>
+        <v>190162</v>
       </c>
       <c r="AA507" t="inlineStr">
         <is>
-          <t>2026-09-23 08:06:57</t>
+          <t>2026-10-08 11:56:10</t>
         </is>
       </c>
       <c r="AB507" t="inlineStr"/>
@@ -78850,14 +78850,14 @@
       </c>
       <c r="X518" t="inlineStr"/>
       <c r="Y518" t="n">
-        <v>257834</v>
+        <v>261745</v>
       </c>
       <c r="Z518" t="n">
-        <v>167737</v>
+        <v>170332</v>
       </c>
       <c r="AA518" t="inlineStr">
         <is>
-          <t>2026-09-15 11:35:44</t>
+          <t>2026-10-08 11:30:31</t>
         </is>
       </c>
       <c r="AB518" t="inlineStr"/>
@@ -78895,7 +78895,7 @@
       </c>
       <c r="AK518" t="inlineStr"/>
       <c r="AL518" t="n">
-        <v>1200</v>
+        <v>1550</v>
       </c>
       <c r="AM518" t="inlineStr"/>
       <c r="AN518" t="inlineStr"/>
@@ -82372,14 +82372,14 @@
       </c>
       <c r="X542" t="inlineStr"/>
       <c r="Y542" t="n">
-        <v>252986</v>
+        <v>255252</v>
       </c>
       <c r="Z542" t="n">
-        <v>164957</v>
+        <v>166348</v>
       </c>
       <c r="AA542" t="inlineStr">
         <is>
-          <t>2026-09-16 14:05:44</t>
+          <t>2026-10-08 12:17:44</t>
         </is>
       </c>
       <c r="AB542" t="inlineStr"/>

--- a/giacenza_schede.xlsx
+++ b/giacenza_schede.xlsx
@@ -2475,14 +2475,14 @@
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>6049</v>
+        <v>7769</v>
       </c>
       <c r="Z14" t="n">
-        <v>3838</v>
+        <v>4856</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-05 07:35:15</t>
+          <t>2026-10-12 07:38:26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
@@ -2630,14 +2630,14 @@
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>5911</v>
+        <v>12119</v>
       </c>
       <c r="Z15" t="n">
-        <v>3760</v>
+        <v>7655</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00:57</t>
+          <t>2026-10-09 11:50:48</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
@@ -10708,14 +10708,14 @@
       </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="n">
-        <v>28196</v>
+        <v>30427</v>
       </c>
       <c r="Z67" t="n">
-        <v>18456</v>
+        <v>19957</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-09-23 08:05:03</t>
+          <t>2026-10-09 11:57:02</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr"/>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>1200</v>
+        <v>3234</v>
       </c>
       <c r="AM67" t="inlineStr"/>
       <c r="AN67" t="inlineStr"/>
@@ -11022,14 +11022,14 @@
       </c>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="n">
-        <v>67502</v>
+        <v>70234</v>
       </c>
       <c r="Z69" t="n">
-        <v>44287</v>
+        <v>46140</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-05 06:25:25</t>
+          <t>2026-10-12 05:55:44</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr"/>
@@ -11340,14 +11340,14 @@
       </c>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="n">
-        <v>101009</v>
+        <v>109431</v>
       </c>
       <c r="Z71" t="n">
-        <v>65521</v>
+        <v>71037</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-09-28 08:06:00</t>
+          <t>2026-10-12 08:07:53</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr"/>
@@ -13504,14 +13504,14 @@
       </c>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="n">
-        <v>103747</v>
+        <v>110601</v>
       </c>
       <c r="Z85" t="n">
-        <v>67153</v>
+        <v>71818</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00:32</t>
+          <t>2026-10-09 11:45:25</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr"/>
@@ -16135,14 +16135,14 @@
       </c>
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="n">
-        <v>112794</v>
+        <v>117581</v>
       </c>
       <c r="Z102" t="n">
-        <v>73389</v>
+        <v>76941</v>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00:45</t>
+          <t>2026-10-09 11:49:36</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
@@ -20965,14 +20965,14 @@
       </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="n">
-        <v>34765</v>
+        <v>38473</v>
       </c>
       <c r="Z134" t="n">
-        <v>22568</v>
+        <v>24431</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-09-12 08:32:50</t>
+          <t>2026-10-09 16:04:41</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr"/>
@@ -21275,14 +21275,14 @@
       </c>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="n">
-        <v>13389</v>
+        <v>19967</v>
       </c>
       <c r="Z136" t="n">
-        <v>8023</v>
+        <v>12680</v>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-07-10 08:55:05</t>
+          <t>2026-10-10 09:19:43</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -21728,14 +21728,14 @@
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="n">
-        <v>35372</v>
+        <v>37122</v>
       </c>
       <c r="Z139" t="n">
-        <v>23093</v>
+        <v>23639</v>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-09-19 13:06:46</t>
+          <t>2026-10-09 15:08:10</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -21883,14 +21883,14 @@
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="n">
-        <v>27187</v>
+        <v>28453</v>
       </c>
       <c r="Z140" t="n">
-        <v>17970</v>
+        <v>18710</v>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-09-19 13:29:42</t>
+          <t>2026-10-10 08:39:41</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -22034,14 +22034,14 @@
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="n">
-        <v>45122</v>
+        <v>47721</v>
       </c>
       <c r="Z141" t="n">
-        <v>28852</v>
+        <v>30528</v>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-08-25 17:11:51</t>
+          <t>2026-10-09 15:30:51</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -23254,14 +23254,14 @@
       </c>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="n">
-        <v>35685</v>
+        <v>39452</v>
       </c>
       <c r="Z149" t="n">
-        <v>23322</v>
+        <v>25786</v>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-09-12 08:33:16</t>
+          <t>2026-10-09 16:05:15</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -23409,14 +23409,14 @@
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="n">
-        <v>33188</v>
+        <v>34681</v>
       </c>
       <c r="Z150" t="n">
-        <v>21627</v>
+        <v>22441</v>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30:05</t>
+          <t>2026-10-10 08:40:13</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -24017,14 +24017,14 @@
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="n">
-        <v>12544</v>
+        <v>19289</v>
       </c>
       <c r="Z154" t="n">
-        <v>8296</v>
+        <v>12568</v>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-07-10 08:55:40</t>
+          <t>2026-10-10 09:20:13</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -24482,14 +24482,14 @@
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="n">
-        <v>51696</v>
+        <v>54870</v>
       </c>
       <c r="Z157" t="n">
-        <v>33900</v>
+        <v>35833</v>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-08-25 17:11:26</t>
+          <t>2026-10-09 15:30:31</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -28361,14 +28361,14 @@
       </c>
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="n">
-        <v>47106</v>
+        <v>50487</v>
       </c>
       <c r="Z182" t="n">
-        <v>29814</v>
+        <v>32321</v>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2026-09-15 07:07:03</t>
+          <t>2026-10-12 05:34:37</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
@@ -30803,14 +30803,14 @@
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="n">
-        <v>224465</v>
+        <v>226789</v>
       </c>
       <c r="Z198" t="n">
-        <v>146337</v>
+        <v>147695</v>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2026-10-05 07:34:57</t>
+          <t>2026-10-12 07:37:42</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -30966,14 +30966,14 @@
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="n">
-        <v>141057</v>
+        <v>142476</v>
       </c>
       <c r="Z199" t="n">
-        <v>91861</v>
+        <v>92773</v>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2026-10-05 05:14:39</t>
+          <t>2026-10-12 04:42:29</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -34324,14 +34324,14 @@
       </c>
       <c r="X221" t="inlineStr"/>
       <c r="Y221" t="n">
-        <v>155695</v>
+        <v>158773</v>
       </c>
       <c r="Z221" t="n">
-        <v>101822</v>
+        <v>103625</v>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-10-02 06:55:36</t>
+          <t>2026-10-12 05:27:27</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr"/>
@@ -38665,14 +38665,14 @@
       </c>
       <c r="X250" t="inlineStr"/>
       <c r="Y250" t="n">
-        <v>140508</v>
+        <v>144947</v>
       </c>
       <c r="Z250" t="n">
-        <v>90842</v>
+        <v>93816</v>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2026-10-02 07:31:25</t>
+          <t>2026-10-12 06:41:36</t>
         </is>
       </c>
       <c r="AB250" t="inlineStr"/>
@@ -39118,14 +39118,14 @@
       </c>
       <c r="X253" t="inlineStr"/>
       <c r="Y253" t="n">
-        <v>86863</v>
+        <v>87498</v>
       </c>
       <c r="Z253" t="n">
-        <v>56320</v>
+        <v>56778</v>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2026-09-14 09:09:05</t>
+          <t>2026-10-12 06:58:51</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr"/>
@@ -39567,14 +39567,14 @@
       </c>
       <c r="X256" t="inlineStr"/>
       <c r="Y256" t="n">
-        <v>241738</v>
+        <v>251313</v>
       </c>
       <c r="Z256" t="n">
-        <v>156970</v>
+        <v>163326</v>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2026-09-28 07:38:08</t>
+          <t>2026-10-12 07:22:46</t>
         </is>
       </c>
       <c r="AB256" t="inlineStr"/>
@@ -41379,14 +41379,14 @@
       </c>
       <c r="X268" t="inlineStr"/>
       <c r="Y268" t="n">
-        <v>238923</v>
+        <v>244114</v>
       </c>
       <c r="Z268" t="n">
-        <v>155405</v>
+        <v>158720</v>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2026-09-28 07:37:52</t>
+          <t>2026-10-12 07:22:27</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr"/>
@@ -45747,14 +45747,14 @@
       </c>
       <c r="X298" t="inlineStr"/>
       <c r="Y298" t="n">
-        <v>159583</v>
+        <v>159895</v>
       </c>
       <c r="Z298" t="n">
-        <v>103889</v>
+        <v>104017</v>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>2026-10-02 06:55:22</t>
+          <t>2026-10-12 05:30:42</t>
         </is>
       </c>
       <c r="AB298" t="inlineStr"/>
@@ -46200,14 +46200,14 @@
       </c>
       <c r="X301" t="inlineStr"/>
       <c r="Y301" t="n">
-        <v>223745</v>
+        <v>225368</v>
       </c>
       <c r="Z301" t="n">
-        <v>145501</v>
+        <v>146631</v>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2026-10-05 06:24:03</t>
+          <t>2026-10-12 05:54:41</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr"/>
@@ -48453,14 +48453,14 @@
       </c>
       <c r="X316" t="inlineStr"/>
       <c r="Y316" t="n">
-        <v>154471</v>
+        <v>155874</v>
       </c>
       <c r="Z316" t="n">
-        <v>101295</v>
+        <v>101964</v>
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>2026-10-02 06:56:01</t>
+          <t>2026-10-12 05:36:26</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr"/>
@@ -49434,14 +49434,14 @@
       </c>
       <c r="X323" t="inlineStr"/>
       <c r="Y323" t="n">
-        <v>168333</v>
+        <v>174816</v>
       </c>
       <c r="Z323" t="n">
-        <v>109845</v>
+        <v>114392</v>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2026-09-09 08:38:24</t>
+          <t>2026-10-09 12:00:35</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr"/>
@@ -53193,14 +53193,14 @@
       </c>
       <c r="X348" t="inlineStr"/>
       <c r="Y348" t="n">
-        <v>488048</v>
+        <v>492303</v>
       </c>
       <c r="Z348" t="n">
-        <v>317700</v>
+        <v>319867</v>
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>2026-09-28 08:05:12</t>
+          <t>2026-10-12 08:06:18</t>
         </is>
       </c>
       <c r="AB348" t="inlineStr"/>
@@ -57266,14 +57266,14 @@
       </c>
       <c r="X375" t="inlineStr"/>
       <c r="Y375" t="n">
-        <v>318461</v>
+        <v>325697</v>
       </c>
       <c r="Z375" t="n">
-        <v>207982</v>
+        <v>212964</v>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
-          <t>2026-09-28 08:06:21</t>
+          <t>2026-10-12 08:10:14</t>
         </is>
       </c>
       <c r="AB375" t="inlineStr"/>
@@ -57719,14 +57719,14 @@
       </c>
       <c r="X378" t="inlineStr"/>
       <c r="Y378" t="n">
-        <v>442120</v>
+        <v>447529</v>
       </c>
       <c r="Z378" t="n">
-        <v>287901</v>
+        <v>291843</v>
       </c>
       <c r="AA378" t="inlineStr">
         <is>
-          <t>2026-09-25 11:00:10</t>
+          <t>2026-10-09 11:45:09</t>
         </is>
       </c>
       <c r="AB378" t="inlineStr"/>
@@ -61307,14 +61307,14 @@
       </c>
       <c r="X402" t="inlineStr"/>
       <c r="Y402" t="n">
-        <v>221289</v>
+        <v>224197</v>
       </c>
       <c r="Z402" t="n">
-        <v>144396</v>
+        <v>146277</v>
       </c>
       <c r="AA402" t="inlineStr">
         <is>
-          <t>2026-09-23 07:57:07</t>
+          <t>2026-10-09 11:58:08</t>
         </is>
       </c>
       <c r="AB402" t="inlineStr"/>
@@ -62366,14 +62366,14 @@
       </c>
       <c r="X409" t="inlineStr"/>
       <c r="Y409" t="n">
-        <v>69362</v>
+        <v>69894</v>
       </c>
       <c r="Z409" t="n">
-        <v>45135</v>
+        <v>45388</v>
       </c>
       <c r="AA409" t="inlineStr">
         <is>
-          <t>2026-07-24 09:11:02</t>
+          <t>2026-10-12 08:18:44</t>
         </is>
       </c>
       <c r="AB409" t="inlineStr"/>
@@ -62676,14 +62676,14 @@
       </c>
       <c r="X411" t="inlineStr"/>
       <c r="Y411" t="n">
-        <v>244233</v>
+        <v>245705</v>
       </c>
       <c r="Z411" t="n">
-        <v>159642</v>
+        <v>160324</v>
       </c>
       <c r="AA411" t="inlineStr">
         <is>
-          <t>2026-09-14 09:09:19</t>
+          <t>2026-10-12 06:59:21</t>
         </is>
       </c>
       <c r="AB411" t="inlineStr"/>
@@ -64806,14 +64806,14 @@
       </c>
       <c r="X425" t="inlineStr"/>
       <c r="Y425" t="n">
-        <v>290292</v>
+        <v>296143</v>
       </c>
       <c r="Z425" t="n">
-        <v>189188</v>
+        <v>192929</v>
       </c>
       <c r="AA425" t="inlineStr">
         <is>
-          <t>2026-09-28 08:05:41</t>
+          <t>2026-10-12 08:09:09</t>
         </is>
       </c>
       <c r="AB425" t="inlineStr"/>
@@ -65867,14 +65867,14 @@
       </c>
       <c r="X432" t="inlineStr"/>
       <c r="Y432" t="n">
-        <v>369393</v>
+        <v>371926</v>
       </c>
       <c r="Z432" t="n">
-        <v>240899</v>
+        <v>242884</v>
       </c>
       <c r="AA432" t="inlineStr">
         <is>
-          <t>2026-10-02 07:31:47</t>
+          <t>2026-10-12 06:42:46</t>
         </is>
       </c>
       <c r="AB432" t="inlineStr"/>
@@ -66097,7 +66097,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -66192,7 +66192,7 @@
       <c r="AD434" t="inlineStr"/>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr"/>
@@ -67785,14 +67785,14 @@
       </c>
       <c r="X445" t="inlineStr"/>
       <c r="Y445" t="n">
-        <v>122715</v>
+        <v>123478</v>
       </c>
       <c r="Z445" t="n">
-        <v>79747</v>
+        <v>80086</v>
       </c>
       <c r="AA445" t="inlineStr">
         <is>
-          <t>2026-07-24 09:11:18</t>
+          <t>2026-10-12 08:18:59</t>
         </is>
       </c>
       <c r="AB445" t="inlineStr"/>
@@ -73865,14 +73865,14 @@
       </c>
       <c r="X485" t="inlineStr"/>
       <c r="Y485" t="n">
-        <v>163569</v>
+        <v>165448</v>
       </c>
       <c r="Z485" t="n">
-        <v>106525</v>
+        <v>107694</v>
       </c>
       <c r="AA485" t="inlineStr">
         <is>
-          <t>2026-10-02 06:55:49</t>
+          <t>2026-10-12 05:28:26</t>
         </is>
       </c>
       <c r="AB485" t="inlineStr"/>
@@ -74473,14 +74473,14 @@
       </c>
       <c r="X489" t="inlineStr"/>
       <c r="Y489" t="n">
-        <v>476217</v>
+        <v>479117</v>
       </c>
       <c r="Z489" t="n">
-        <v>310440</v>
+        <v>312261</v>
       </c>
       <c r="AA489" t="inlineStr">
         <is>
-          <t>2026-10-05 05:14:05</t>
+          <t>2026-10-12 04:41:50</t>
         </is>
       </c>
       <c r="AB489" t="inlineStr"/>
@@ -79001,14 +79001,14 @@
       </c>
       <c r="X519" t="inlineStr"/>
       <c r="Y519" t="n">
-        <v>561059</v>
+        <v>563195</v>
       </c>
       <c r="Z519" t="n">
-        <v>366096</v>
+        <v>367358</v>
       </c>
       <c r="AA519" t="inlineStr">
         <is>
-          <t>2026-10-05 05:14:20</t>
+          <t>2026-10-12 04:42:11</t>
         </is>
       </c>
       <c r="AB519" t="inlineStr"/>
@@ -79458,14 +79458,14 @@
       </c>
       <c r="X522" t="inlineStr"/>
       <c r="Y522" t="n">
-        <v>421078</v>
+        <v>423307</v>
       </c>
       <c r="Z522" t="n">
-        <v>273800</v>
+        <v>275226</v>
       </c>
       <c r="AA522" t="inlineStr">
         <is>
-          <t>2026-09-23 07:55:32</t>
+          <t>2026-10-09 06:46:44</t>
         </is>
       </c>
       <c r="AB522" t="inlineStr"/>
@@ -79928,7 +79928,7 @@
       <c r="AB525" t="inlineStr"/>
       <c r="AC525" t="inlineStr">
         <is>
-          <t>MOBILE NEW BELL - SIRA SLIM</t>
+          <t>WINTEK QUEEN 2</t>
         </is>
       </c>
       <c r="AD525" t="inlineStr"/>
@@ -80336,14 +80336,14 @@
       </c>
       <c r="X528" t="inlineStr"/>
       <c r="Y528" t="n">
-        <v>685365</v>
+        <v>687228</v>
       </c>
       <c r="Z528" t="n">
-        <v>446872</v>
+        <v>448121</v>
       </c>
       <c r="AA528" t="inlineStr">
         <is>
-          <t>2026-10-05 07:34:41</t>
+          <t>2026-10-12 07:37:07</t>
         </is>
       </c>
       <c r="AB528" t="inlineStr"/>
@@ -81369,14 +81369,14 @@
       </c>
       <c r="X535" t="inlineStr"/>
       <c r="Y535" t="n">
-        <v>1357601</v>
+        <v>1359915</v>
       </c>
       <c r="Z535" t="n">
-        <v>884684</v>
+        <v>886186</v>
       </c>
       <c r="AA535" t="inlineStr">
         <is>
-          <t>2026-10-05 06:22:13</t>
+          <t>2026-10-12 05:54:28</t>
         </is>
       </c>
       <c r="AB535" t="inlineStr"/>

--- a/giacenza_schede.xlsx
+++ b/giacenza_schede.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -738,9 +738,17 @@
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>MOBILE WIN-TEK QUEEN</t>
+        </is>
+      </c>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
@@ -925,7 +933,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1012,9 +1020,17 @@
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>MOBILE NEW BELL - SIRA SLIM</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
@@ -1136,14 +1152,14 @@
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>8823</v>
+        <v>14394</v>
       </c>
       <c r="Z5" t="n">
-        <v>5442</v>
+        <v>9505</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-29 10:58:23</t>
+          <t>2026-10-13 07:57:08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1226,7 +1242,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SNAITECH WNG</t>
+          <t>NTS Network SpA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1509,7 +1525,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1596,9 +1612,17 @@
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>MOBILE NEW BELL - SIRA SLIM</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr">
@@ -2320,14 +2344,14 @@
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>3193</v>
+        <v>9257</v>
       </c>
       <c r="Z13" t="n">
-        <v>2211</v>
+        <v>6286</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-02 13:17:20</t>
+          <t>2026-10-12 12:44:34</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
@@ -2785,14 +2809,14 @@
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>2164</v>
+        <v>6207</v>
       </c>
       <c r="Z16" t="n">
-        <v>1486</v>
+        <v>4060</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:31</t>
+          <t>2026-10-13 08:23:17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
@@ -3087,14 +3111,14 @@
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>11996</v>
+        <v>19793</v>
       </c>
       <c r="Z18" t="n">
-        <v>7585</v>
+        <v>12849</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-02 09:39:49</t>
+          <t>2026-10-15 10:03:06</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
@@ -3246,14 +3270,14 @@
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>2758</v>
+        <v>8433</v>
       </c>
       <c r="Z19" t="n">
-        <v>2134</v>
+        <v>5688</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-29 11:08:19</t>
+          <t>2026-10-13 08:22:49</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
@@ -3719,14 +3743,14 @@
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>56491</v>
+        <v>60420</v>
       </c>
       <c r="Z22" t="n">
-        <v>37019</v>
+        <v>39386</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-05 09:53:41</t>
+          <t>2026-10-12 09:06:06</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
@@ -4337,14 +4361,14 @@
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>48945</v>
+        <v>54054</v>
       </c>
       <c r="Z26" t="n">
-        <v>32211</v>
+        <v>35062</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-06 12:27:13</t>
+          <t>2026-10-13 13:46:38</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -4498,14 +4522,14 @@
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>76977</v>
+        <v>81105</v>
       </c>
       <c r="Z27" t="n">
-        <v>50268</v>
+        <v>52602</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-07 12:45:24</t>
+          <t>2026-10-15 12:34:05</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -4861,7 +4885,7 @@
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
@@ -5029,7 +5053,11 @@
       <c r="AQ30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>YN06763727Z</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>MAGIC DREAMS</t>
@@ -5047,7 +5075,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MD20100</t>
+          <t>YN06763727Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5057,7 +5085,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SNAITECH WNG</t>
+          <t>NTS Network SpA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5077,13 +5105,21 @@
       <c r="L31" t="n">
         <v>65</v>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>C11E03893813R</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>C11D03936957R</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t xml:space="preserve">NET SRL  </t>
@@ -5253,14 +5289,14 @@
       </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="n">
-        <v>27771</v>
+        <v>30665</v>
       </c>
       <c r="Z32" t="n">
-        <v>18217</v>
+        <v>20067</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:17</t>
+          <t>2026-10-14 11:21:21</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -5311,7 +5347,11 @@
       <c r="AQ32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>YN06763726A</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>SPIN PARADISE G640S</t>
@@ -5329,7 +5369,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SP20394</t>
+          <t>YN06763726A</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5339,7 +5379,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SNAITECH WNG</t>
+          <t>NTS Network SpA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5359,13 +5399,21 @@
       <c r="L33" t="n">
         <v>65</v>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>C11E03893812R</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>C11D03936922R</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t xml:space="preserve">NET SRL  </t>
@@ -6171,14 +6219,14 @@
       </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
-        <v>68579</v>
+        <v>72843</v>
       </c>
       <c r="Z38" t="n">
-        <v>44807</v>
+        <v>47438</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-06 06:24:28</t>
+          <t>2026-10-13 07:21:25</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
@@ -6330,14 +6378,14 @@
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>16166</v>
+        <v>18160</v>
       </c>
       <c r="Z39" t="n">
-        <v>10733</v>
+        <v>11949</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-28 12:15:02</t>
+          <t>2026-10-12 12:37:40</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -6491,14 +6539,14 @@
       </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="n">
-        <v>47446</v>
+        <v>51392</v>
       </c>
       <c r="Z40" t="n">
-        <v>31370</v>
+        <v>33860</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-28 10:36:37</t>
+          <t>2026-10-12 10:06:50</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
@@ -7427,14 +7475,14 @@
       </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="n">
-        <v>32733</v>
+        <v>34551</v>
       </c>
       <c r="Z46" t="n">
-        <v>21400</v>
+        <v>22542</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-05 12:04:00</t>
+          <t>2026-10-12 11:31:05</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
@@ -7584,14 +7632,14 @@
       </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="n">
-        <v>35404</v>
+        <v>39422</v>
       </c>
       <c r="Z47" t="n">
-        <v>22910</v>
+        <v>25688</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-09-28 10:36:52</t>
+          <t>2026-10-12 10:07:05</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
@@ -7739,14 +7787,14 @@
       </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="n">
-        <v>19011</v>
+        <v>20704</v>
       </c>
       <c r="Z48" t="n">
-        <v>12502</v>
+        <v>13482</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-05 12:04:13</t>
+          <t>2026-10-12 11:31:19</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
@@ -8049,14 +8097,14 @@
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="n">
-        <v>62960</v>
+        <v>66461</v>
       </c>
       <c r="Z50" t="n">
-        <v>41318</v>
+        <v>43493</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-28 10:36:04</t>
+          <t>2026-10-12 10:06:08</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
@@ -8208,14 +8256,14 @@
       </c>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="n">
-        <v>30325</v>
+        <v>32382</v>
       </c>
       <c r="Z51" t="n">
-        <v>19939</v>
+        <v>21496</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-05 12:03:46</t>
+          <t>2026-10-12 11:30:34</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
@@ -8363,14 +8411,14 @@
       </c>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="n">
-        <v>43795</v>
+        <v>47109</v>
       </c>
       <c r="Z52" t="n">
-        <v>28821</v>
+        <v>30817</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-06 12:27:27</t>
+          <t>2026-10-13 13:46:11</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
@@ -8838,14 +8886,14 @@
       </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="n">
-        <v>28660</v>
+        <v>30214</v>
       </c>
       <c r="Z55" t="n">
-        <v>18505</v>
+        <v>19610</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-05 11:56:41</t>
+          <t>2026-10-12 11:27:33</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr"/>
@@ -9152,14 +9200,14 @@
       </c>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="n">
-        <v>22238</v>
+        <v>25183</v>
       </c>
       <c r="Z57" t="n">
-        <v>14456</v>
+        <v>16482</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-09-29 11:10:39</t>
+          <t>2026-10-13 09:26:33</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr"/>
@@ -9197,7 +9245,7 @@
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>1070</v>
+        <v>1000</v>
       </c>
       <c r="AM57" t="inlineStr"/>
       <c r="AN57" t="inlineStr"/>
@@ -9617,14 +9665,14 @@
       </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="n">
-        <v>93735</v>
+        <v>99539</v>
       </c>
       <c r="Z60" t="n">
-        <v>61288</v>
+        <v>65028</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-09-28 10:36:21</t>
+          <t>2026-10-12 10:06:26</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
@@ -10241,14 +10289,14 @@
       </c>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="n">
-        <v>32010</v>
+        <v>35002</v>
       </c>
       <c r="Z64" t="n">
-        <v>20960</v>
+        <v>22622</v>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-09-23 09:37:41</t>
+          <t>2026-10-12 09:34:02</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr"/>
@@ -10555,14 +10603,14 @@
       </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="n">
-        <v>32243</v>
+        <v>34227</v>
       </c>
       <c r="Z66" t="n">
-        <v>21043</v>
+        <v>22228</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-05 11:58:09</t>
+          <t>2026-10-12 11:28:23</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr"/>
@@ -11179,14 +11227,14 @@
       </c>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="n">
-        <v>37109</v>
+        <v>40185</v>
       </c>
       <c r="Z70" t="n">
-        <v>24279</v>
+        <v>26040</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-01 08:57:08</t>
+          <t>2026-10-15 08:01:14</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr"/>
@@ -12896,14 +12944,14 @@
       </c>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="n">
-        <v>69799</v>
+        <v>73352</v>
       </c>
       <c r="Z81" t="n">
-        <v>45433</v>
+        <v>47684</v>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-01 08:47:31</t>
+          <t>2026-10-15 08:02:36</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr"/>
@@ -13351,14 +13399,14 @@
       </c>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="n">
-        <v>54319</v>
+        <v>55689</v>
       </c>
       <c r="Z84" t="n">
-        <v>34599</v>
+        <v>35947</v>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-05 11:56:16</t>
+          <t>2026-10-12 11:27:03</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr"/>
@@ -14136,14 +14184,14 @@
       </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="n">
-        <v>65948</v>
+        <v>69055</v>
       </c>
       <c r="Z89" t="n">
-        <v>42855</v>
+        <v>44626</v>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-01 06:45:40</t>
+          <t>2026-10-13 06:29:33</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr"/>
@@ -14446,14 +14494,14 @@
       </c>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="n">
-        <v>130461</v>
+        <v>132106</v>
       </c>
       <c r="Z91" t="n">
-        <v>84729</v>
+        <v>85781</v>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-06 12:40:45</t>
+          <t>2026-10-13 11:37:30</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr"/>
@@ -14756,14 +14804,14 @@
       </c>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="n">
-        <v>34871</v>
+        <v>36985</v>
       </c>
       <c r="Z93" t="n">
-        <v>22382</v>
+        <v>24121</v>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-01 08:52:05</t>
+          <t>2026-10-15 07:59:54</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
@@ -15533,14 +15581,14 @@
       </c>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="n">
-        <v>52050</v>
+        <v>55030</v>
       </c>
       <c r="Z98" t="n">
-        <v>33752</v>
+        <v>36085</v>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-09-29 07:32:32</t>
+          <t>2026-10-13 05:58:45</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr"/>
@@ -15835,14 +15883,14 @@
       </c>
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="n">
-        <v>12516</v>
+        <v>13034</v>
       </c>
       <c r="Z100" t="n">
-        <v>8651</v>
+        <v>8828</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-01 14:18:24</t>
+          <t>2026-10-15 07:06:28</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr"/>
@@ -16592,14 +16640,14 @@
       </c>
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="n">
-        <v>39782</v>
+        <v>43573</v>
       </c>
       <c r="Z105" t="n">
-        <v>26375</v>
+        <v>28730</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-08-04 09:17:03</t>
+          <t>2026-10-13 08:07:40</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
@@ -16747,14 +16795,14 @@
       </c>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="n">
-        <v>11908</v>
+        <v>13223</v>
       </c>
       <c r="Z106" t="n">
-        <v>7692</v>
+        <v>8676</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-01 14:16:00</t>
+          <t>2026-10-15 07:05:35</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr"/>
@@ -18467,7 +18515,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>BAR FIORI</t>
+          <t>WINGAMING SRL - DEPOSITO GUASTI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -18551,14 +18599,14 @@
       </c>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="n">
-        <v>25597</v>
+        <v>26177</v>
       </c>
       <c r="Z118" t="n">
-        <v>16565</v>
+        <v>16864</v>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-06 11:19:16</t>
+          <t>2026-10-13 11:11:25</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr"/>
@@ -18570,30 +18618,18 @@
       <c r="AD118" t="inlineStr"/>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AF118" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AG118" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>E004292</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>EA580046885R</t>
-        </is>
-      </c>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr"/>
       <c r="AK118" t="inlineStr"/>
       <c r="AL118" t="n">
         <v>0</v>
@@ -18601,11 +18637,7 @@
       <c r="AM118" t="inlineStr"/>
       <c r="AN118" t="inlineStr"/>
       <c r="AO118" t="inlineStr"/>
-      <c r="AP118" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
+      <c r="AP118" t="inlineStr"/>
       <c r="AQ118" t="inlineStr"/>
     </row>
     <row r="119">
@@ -18626,7 +18658,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -18729,7 +18761,7 @@
       <c r="AD119" t="inlineStr"/>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr"/>
@@ -20023,14 +20055,14 @@
       </c>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="n">
-        <v>25852</v>
+        <v>26741</v>
       </c>
       <c r="Z128" t="n">
-        <v>16727</v>
+        <v>17248</v>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-09-28 11:30:11</t>
+          <t>2026-10-14 11:17:58</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr"/>
@@ -25102,14 +25134,14 @@
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="n">
-        <v>201135</v>
+        <v>202842</v>
       </c>
       <c r="Z161" t="n">
-        <v>130688</v>
+        <v>131865</v>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-10-06 06:24:15</t>
+          <t>2026-10-13 07:23:59</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -25420,14 +25452,14 @@
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="n">
-        <v>40440</v>
+        <v>41076</v>
       </c>
       <c r="Z163" t="n">
-        <v>26115</v>
+        <v>26724</v>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-10-06 11:17:29</t>
+          <t>2026-10-13 11:10:45</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -26350,14 +26382,14 @@
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="n">
-        <v>49663</v>
+        <v>51184</v>
       </c>
       <c r="Z169" t="n">
-        <v>32429</v>
+        <v>33633</v>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2026-10-01 08:50:33</t>
+          <t>2026-10-15 07:57:17</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -27574,14 +27606,14 @@
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="n">
-        <v>373008</v>
+        <v>377387</v>
       </c>
       <c r="Z177" t="n">
-        <v>242967</v>
+        <v>245620</v>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2026-10-05 09:52:34</t>
+          <t>2026-10-12 09:06:45</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -27733,14 +27765,14 @@
       </c>
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="n">
-        <v>71436</v>
+        <v>76977</v>
       </c>
       <c r="Z178" t="n">
-        <v>46150</v>
+        <v>49707</v>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2026-10-05 10:16:57</t>
+          <t>2026-10-12 09:45:18</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr"/>
@@ -27892,14 +27924,14 @@
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="n">
-        <v>146207</v>
+        <v>149218</v>
       </c>
       <c r="Z179" t="n">
-        <v>95368</v>
+        <v>97359</v>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-07-13 08:27:25</t>
+          <t>2026-10-13 17:25:21</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -28516,14 +28548,14 @@
       </c>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="n">
-        <v>111334</v>
+        <v>114222</v>
       </c>
       <c r="Z183" t="n">
-        <v>72525</v>
+        <v>74240</v>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-10-02 09:22:09</t>
+          <t>2026-10-15 11:25:04</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -28744,7 +28776,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>BAR NORGE</t>
+          <t>WINGAMING SRL - DEPOSITO GUASTI</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -28843,30 +28875,18 @@
       <c r="AD185" t="inlineStr"/>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AF185" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG185" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>E036784</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>EA560014229R</t>
-        </is>
-      </c>
+      <c r="AI185" t="inlineStr"/>
+      <c r="AJ185" t="inlineStr"/>
       <c r="AK185" t="inlineStr"/>
       <c r="AL185" t="n">
         <v>0</v>
@@ -28874,11 +28894,7 @@
       <c r="AM185" t="inlineStr"/>
       <c r="AN185" t="inlineStr"/>
       <c r="AO185" t="inlineStr"/>
-      <c r="AP185" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
+      <c r="AP185" t="inlineStr"/>
       <c r="AQ185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -29305,14 +29321,14 @@
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="n">
-        <v>230743</v>
+        <v>234256</v>
       </c>
       <c r="Z188" t="n">
-        <v>150628</v>
+        <v>152247</v>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-10-05 10:17:25</t>
+          <t>2026-10-12 09:45:53</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -30028,14 +30044,14 @@
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="n">
-        <v>478165</v>
+        <v>481230</v>
       </c>
       <c r="Z193" t="n">
-        <v>311635</v>
+        <v>313480</v>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2026-08-31 08:37:47</t>
+          <t>2026-10-14 11:21:49</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -30187,14 +30203,14 @@
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="n">
-        <v>283083</v>
+        <v>285499</v>
       </c>
       <c r="Z194" t="n">
-        <v>184394</v>
+        <v>186309</v>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2026-10-01 06:46:40</t>
+          <t>2026-10-13 06:29:46</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -30262,7 +30278,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO GUASTI</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -30342,10 +30358,10 @@
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="n">
-        <v>48351</v>
+        <v>50255</v>
       </c>
       <c r="Z195" t="n">
-        <v>30641</v>
+        <v>32414</v>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
@@ -30361,7 +30377,7 @@
       <c r="AD195" t="inlineStr"/>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr"/>
@@ -30485,14 +30501,14 @@
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="n">
-        <v>250789</v>
+        <v>253398</v>
       </c>
       <c r="Z196" t="n">
-        <v>163587</v>
+        <v>165187</v>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2026-10-05 09:53:00</t>
+          <t>2026-10-12 09:05:03</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -31765,14 +31781,14 @@
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="n">
-        <v>55520</v>
+        <v>57395</v>
       </c>
       <c r="Z204" t="n">
-        <v>36058</v>
+        <v>37228</v>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2026-09-17 13:05:27</t>
+          <t>2026-10-13 07:33:31</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -33267,14 +33283,14 @@
       </c>
       <c r="X214" t="inlineStr"/>
       <c r="Y214" t="n">
-        <v>144848</v>
+        <v>147057</v>
       </c>
       <c r="Z214" t="n">
-        <v>94376</v>
+        <v>95627</v>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2026-09-15 09:42:10</t>
+          <t>2026-10-13 11:36:38</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr"/>
@@ -33418,14 +33434,14 @@
       </c>
       <c r="X215" t="inlineStr"/>
       <c r="Y215" t="n">
-        <v>160789</v>
+        <v>162488</v>
       </c>
       <c r="Z215" t="n">
-        <v>104732</v>
+        <v>105868</v>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2026-10-07 10:32:35</t>
+          <t>2026-10-14 11:20:57</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr"/>
@@ -34022,14 +34038,14 @@
       </c>
       <c r="X219" t="inlineStr"/>
       <c r="Y219" t="n">
-        <v>148044</v>
+        <v>149415</v>
       </c>
       <c r="Z219" t="n">
-        <v>96239</v>
+        <v>97125</v>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2026-10-01 10:13:40</t>
+          <t>2026-10-15 09:09:32</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr"/>
@@ -35309,7 +35325,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -35404,7 +35420,7 @@
       <c r="AD228" t="inlineStr"/>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr"/>
@@ -35597,7 +35613,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>BAR FIORI</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -35692,18 +35708,30 @@
       <c r="AD230" t="inlineStr"/>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr"/>
-      <c r="AG230" t="inlineStr"/>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AF230" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>0</v>
+      </c>
       <c r="AH230" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI230" t="inlineStr"/>
-      <c r="AJ230" t="inlineStr"/>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>E004292</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>EA580046885R</t>
+        </is>
+      </c>
       <c r="AK230" t="inlineStr"/>
       <c r="AL230" t="n">
         <v>0</v>
@@ -35711,7 +35739,11 @@
       <c r="AM230" t="inlineStr"/>
       <c r="AN230" t="inlineStr"/>
       <c r="AO230" t="inlineStr"/>
-      <c r="AP230" t="inlineStr"/>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
       <c r="AQ230" t="inlineStr"/>
     </row>
     <row r="231">
@@ -35808,14 +35840,14 @@
       </c>
       <c r="X231" t="inlineStr"/>
       <c r="Y231" t="n">
-        <v>75999</v>
+        <v>79670</v>
       </c>
       <c r="Z231" t="n">
-        <v>49342</v>
+        <v>51827</v>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2026-05-13 11:02:02</t>
+          <t>2026-10-13 06:30:06</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr"/>
@@ -36110,14 +36142,14 @@
       </c>
       <c r="X233" t="inlineStr"/>
       <c r="Y233" t="n">
-        <v>85101</v>
+        <v>85997</v>
       </c>
       <c r="Z233" t="n">
-        <v>55288</v>
+        <v>55921</v>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:29</t>
+          <t>2026-10-13 11:10:59</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr"/>
@@ -36412,14 +36444,14 @@
       </c>
       <c r="X235" t="inlineStr"/>
       <c r="Y235" t="n">
-        <v>55585</v>
+        <v>56567</v>
       </c>
       <c r="Z235" t="n">
-        <v>36141</v>
+        <v>36690</v>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2026-09-28 12:01:45</t>
+          <t>2026-10-14 11:15:41</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr"/>
@@ -36861,14 +36893,14 @@
       </c>
       <c r="X238" t="inlineStr"/>
       <c r="Y238" t="n">
-        <v>318050</v>
+        <v>324412</v>
       </c>
       <c r="Z238" t="n">
-        <v>207241</v>
+        <v>211524</v>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2026-09-28 09:30:34</t>
+          <t>2026-10-12 09:05:23</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr"/>
@@ -37016,14 +37048,14 @@
       </c>
       <c r="X239" t="inlineStr"/>
       <c r="Y239" t="n">
-        <v>165627</v>
+        <v>167982</v>
       </c>
       <c r="Z239" t="n">
-        <v>107558</v>
+        <v>108846</v>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-09-29 12:09:02</t>
+          <t>2026-10-13 08:07:08</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr"/>
@@ -37363,7 +37395,7 @@
       </c>
       <c r="AK241" t="inlineStr"/>
       <c r="AL241" t="n">
-        <v>2071</v>
+        <v>2000</v>
       </c>
       <c r="AM241" t="inlineStr"/>
       <c r="AN241" t="inlineStr"/>
@@ -37469,14 +37501,14 @@
       </c>
       <c r="X242" t="inlineStr"/>
       <c r="Y242" t="n">
-        <v>254747</v>
+        <v>257704</v>
       </c>
       <c r="Z242" t="n">
-        <v>165625</v>
+        <v>167578</v>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2026-10-02 13:17:50</t>
+          <t>2026-10-12 12:44:35</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr"/>
@@ -37997,7 +38029,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>WINGAMING SRL</t>
+          <t>BAR NORGE</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -38086,24 +38118,36 @@
       <c r="AB246" t="inlineStr"/>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>MOBILE WIN-TEK QUEEN</t>
+          <t>MOBILE NEW BELL - SIRA SLIM</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr"/>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr"/>
-      <c r="AG246" t="inlineStr"/>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AF246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>0</v>
+      </c>
       <c r="AH246" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI246" t="inlineStr"/>
-      <c r="AJ246" t="inlineStr"/>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>E036784</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>EA560014229R</t>
+        </is>
+      </c>
       <c r="AK246" t="inlineStr"/>
       <c r="AL246" t="n">
         <v>0</v>
@@ -38111,7 +38155,11 @@
       <c r="AM246" t="inlineStr"/>
       <c r="AN246" t="inlineStr"/>
       <c r="AO246" t="inlineStr"/>
-      <c r="AP246" t="inlineStr"/>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
       <c r="AQ246" t="inlineStr"/>
     </row>
     <row r="247">
@@ -38208,14 +38256,14 @@
       </c>
       <c r="X247" t="inlineStr"/>
       <c r="Y247" t="n">
-        <v>189965</v>
+        <v>192681</v>
       </c>
       <c r="Z247" t="n">
-        <v>123649</v>
+        <v>125685</v>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2026-10-01 11:46:45</t>
+          <t>2026-10-15 11:37:16</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr"/>
@@ -38514,14 +38562,14 @@
       </c>
       <c r="X249" t="inlineStr"/>
       <c r="Y249" t="n">
-        <v>165045</v>
+        <v>168273</v>
       </c>
       <c r="Z249" t="n">
-        <v>107586</v>
+        <v>109828</v>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2026-10-01 06:47:59</t>
+          <t>2026-10-13 06:29:13</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr"/>
@@ -39420,14 +39468,14 @@
       </c>
       <c r="X255" t="inlineStr"/>
       <c r="Y255" t="n">
-        <v>138076</v>
+        <v>140172</v>
       </c>
       <c r="Z255" t="n">
-        <v>89518</v>
+        <v>91193</v>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2026-10-05 12:02:29</t>
+          <t>2026-10-12 11:30:09</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr"/>
@@ -39722,14 +39770,14 @@
       </c>
       <c r="X257" t="inlineStr"/>
       <c r="Y257" t="n">
-        <v>170622</v>
+        <v>172008</v>
       </c>
       <c r="Z257" t="n">
-        <v>110308</v>
+        <v>111354</v>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2026-10-01 10:15:47</t>
+          <t>2026-10-15 09:10:20</t>
         </is>
       </c>
       <c r="AB257" t="inlineStr"/>
@@ -39877,14 +39925,14 @@
       </c>
       <c r="X258" t="inlineStr"/>
       <c r="Y258" t="n">
-        <v>112548</v>
+        <v>114608</v>
       </c>
       <c r="Z258" t="n">
-        <v>73328</v>
+        <v>74500</v>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2026-10-01 08:58:59</t>
+          <t>2026-10-15 07:56:53</t>
         </is>
       </c>
       <c r="AB258" t="inlineStr"/>
@@ -40179,14 +40227,14 @@
       </c>
       <c r="X260" t="inlineStr"/>
       <c r="Y260" t="n">
-        <v>91968</v>
+        <v>95202</v>
       </c>
       <c r="Z260" t="n">
-        <v>59845</v>
+        <v>61878</v>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-09-16 10:32:41</t>
+          <t>2026-10-15 11:20:06</t>
         </is>
       </c>
       <c r="AB260" t="inlineStr"/>
@@ -40224,7 +40272,7 @@
       </c>
       <c r="AK260" t="inlineStr"/>
       <c r="AL260" t="n">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="AM260" t="inlineStr"/>
       <c r="AN260" t="inlineStr"/>
@@ -40926,14 +40974,14 @@
       </c>
       <c r="X265" t="inlineStr"/>
       <c r="Y265" t="n">
-        <v>60267</v>
+        <v>61114</v>
       </c>
       <c r="Z265" t="n">
-        <v>39131</v>
+        <v>39576</v>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15:04</t>
+          <t>2026-10-13 11:10:28</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr"/>
@@ -41534,14 +41582,14 @@
       </c>
       <c r="X269" t="inlineStr"/>
       <c r="Y269" t="n">
-        <v>284219</v>
+        <v>286646</v>
       </c>
       <c r="Z269" t="n">
-        <v>184950</v>
+        <v>186160</v>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2026-10-07 12:45:00</t>
+          <t>2026-10-15 12:31:39</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr"/>
@@ -43558,14 +43606,14 @@
       </c>
       <c r="X283" t="inlineStr"/>
       <c r="Y283" t="n">
-        <v>218986</v>
+        <v>222729</v>
       </c>
       <c r="Z283" t="n">
-        <v>142927</v>
+        <v>145308</v>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>2026-10-06 12:31:13</t>
+          <t>2026-10-13 11:35:05</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr"/>
@@ -46355,14 +46403,14 @@
       </c>
       <c r="X302" t="inlineStr"/>
       <c r="Y302" t="n">
-        <v>146632</v>
+        <v>148780</v>
       </c>
       <c r="Z302" t="n">
-        <v>95236</v>
+        <v>96762</v>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>2026-09-29 12:10:04</t>
+          <t>2026-10-13 08:07:23</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr"/>
@@ -47404,14 +47452,14 @@
       </c>
       <c r="X309" t="inlineStr"/>
       <c r="Y309" t="n">
-        <v>212521</v>
+        <v>215399</v>
       </c>
       <c r="Z309" t="n">
-        <v>138472</v>
+        <v>140237</v>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>2026-10-01 11:47:01</t>
+          <t>2026-10-15 11:37:29</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr"/>
@@ -47865,14 +47913,14 @@
       </c>
       <c r="X312" t="inlineStr"/>
       <c r="Y312" t="n">
-        <v>199443</v>
+        <v>203461</v>
       </c>
       <c r="Z312" t="n">
-        <v>130056</v>
+        <v>132851</v>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2026-10-05 10:17:37</t>
+          <t>2026-10-12 09:46:11</t>
         </is>
       </c>
       <c r="AB312" t="inlineStr"/>
@@ -49887,14 +49935,14 @@
       </c>
       <c r="X326" t="inlineStr"/>
       <c r="Y326" t="n">
-        <v>138631</v>
+        <v>140813</v>
       </c>
       <c r="Z326" t="n">
-        <v>90210</v>
+        <v>91458</v>
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>2026-09-29 07:31:13</t>
+          <t>2026-10-13 05:58:05</t>
         </is>
       </c>
       <c r="AB326" t="inlineStr"/>
@@ -50197,14 +50245,14 @@
       </c>
       <c r="X328" t="inlineStr"/>
       <c r="Y328" t="n">
-        <v>128427</v>
+        <v>131968</v>
       </c>
       <c r="Z328" t="n">
-        <v>84045</v>
+        <v>86323</v>
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2026-09-29 07:31:38</t>
+          <t>2026-10-13 05:58:19</t>
         </is>
       </c>
       <c r="AB328" t="inlineStr"/>
@@ -50352,14 +50400,14 @@
       </c>
       <c r="X329" t="inlineStr"/>
       <c r="Y329" t="n">
-        <v>289532</v>
+        <v>293349</v>
       </c>
       <c r="Z329" t="n">
-        <v>189170</v>
+        <v>191771</v>
       </c>
       <c r="AA329" t="inlineStr">
         <is>
-          <t>2026-10-02 09:39:34</t>
+          <t>2026-10-15 10:02:54</t>
         </is>
       </c>
       <c r="AB329" t="inlineStr"/>
@@ -51099,14 +51147,14 @@
       </c>
       <c r="X334" t="inlineStr"/>
       <c r="Y334" t="n">
-        <v>199298</v>
+        <v>200793</v>
       </c>
       <c r="Z334" t="n">
-        <v>130302</v>
+        <v>131396</v>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>2026-10-01 10:14:03</t>
+          <t>2026-10-15 09:09:07</t>
         </is>
       </c>
       <c r="AB334" t="inlineStr"/>
@@ -52291,14 +52339,14 @@
       </c>
       <c r="X342" t="inlineStr"/>
       <c r="Y342" t="n">
-        <v>216683</v>
+        <v>221409</v>
       </c>
       <c r="Z342" t="n">
-        <v>140538</v>
+        <v>144178</v>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2026-10-02 09:37:59</t>
+          <t>2026-10-15 10:02:09</t>
         </is>
       </c>
       <c r="AB342" t="inlineStr"/>
@@ -53042,14 +53090,14 @@
       </c>
       <c r="X347" t="inlineStr"/>
       <c r="Y347" t="n">
-        <v>567674</v>
+        <v>571332</v>
       </c>
       <c r="Z347" t="n">
-        <v>369210</v>
+        <v>371757</v>
       </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>2026-10-07 12:44:33</t>
+          <t>2026-10-15 12:30:32</t>
         </is>
       </c>
       <c r="AB347" t="inlineStr"/>
@@ -53348,14 +53396,14 @@
       </c>
       <c r="X349" t="inlineStr"/>
       <c r="Y349" t="n">
-        <v>518133</v>
+        <v>521436</v>
       </c>
       <c r="Z349" t="n">
-        <v>337741</v>
+        <v>339599</v>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2026-10-06 06:24:39</t>
+          <t>2026-10-13 07:20:45</t>
         </is>
       </c>
       <c r="AB349" t="inlineStr"/>
@@ -55442,14 +55490,14 @@
       </c>
       <c r="X363" t="inlineStr"/>
       <c r="Y363" t="n">
-        <v>297577</v>
+        <v>300211</v>
       </c>
       <c r="Z363" t="n">
-        <v>193458</v>
+        <v>195248</v>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>2026-10-06 06:23:56</t>
+          <t>2026-10-13 07:23:24</t>
         </is>
       </c>
       <c r="AB363" t="inlineStr"/>
@@ -59082,14 +59130,14 @@
       </c>
       <c r="X387" t="inlineStr"/>
       <c r="Y387" t="n">
-        <v>324615</v>
+        <v>326145</v>
       </c>
       <c r="Z387" t="n">
-        <v>211409</v>
+        <v>212415</v>
       </c>
       <c r="AA387" t="inlineStr">
         <is>
-          <t>2026-09-29 10:09:19</t>
+          <t>2026-10-13 10:19:56</t>
         </is>
       </c>
       <c r="AB387" t="inlineStr"/>
@@ -59384,14 +59432,14 @@
       </c>
       <c r="X389" t="inlineStr"/>
       <c r="Y389" t="n">
-        <v>257224</v>
+        <v>259965</v>
       </c>
       <c r="Z389" t="n">
-        <v>167245</v>
+        <v>169086</v>
       </c>
       <c r="AA389" t="inlineStr">
         <is>
-          <t>2026-09-29 11:13:01</t>
+          <t>2026-10-13 09:26:03</t>
         </is>
       </c>
       <c r="AB389" t="inlineStr"/>
@@ -60266,14 +60314,14 @@
       </c>
       <c r="X395" t="inlineStr"/>
       <c r="Y395" t="n">
-        <v>414341</v>
+        <v>416242</v>
       </c>
       <c r="Z395" t="n">
-        <v>269697</v>
+        <v>270844</v>
       </c>
       <c r="AA395" t="inlineStr">
         <is>
-          <t>2026-10-06 12:40:06</t>
+          <t>2026-10-13 11:35:29</t>
         </is>
       </c>
       <c r="AB395" t="inlineStr"/>
@@ -60858,14 +60906,14 @@
       </c>
       <c r="X399" t="inlineStr"/>
       <c r="Y399" t="n">
-        <v>245125</v>
+        <v>247309</v>
       </c>
       <c r="Z399" t="n">
-        <v>159877</v>
+        <v>161434</v>
       </c>
       <c r="AA399" t="inlineStr">
         <is>
-          <t>2026-10-05 11:56:04</t>
+          <t>2026-10-12 11:26:44</t>
         </is>
       </c>
       <c r="AB399" t="inlineStr"/>
@@ -61005,14 +61053,14 @@
       </c>
       <c r="X400" t="inlineStr"/>
       <c r="Y400" t="n">
-        <v>443172</v>
+        <v>446732</v>
       </c>
       <c r="Z400" t="n">
-        <v>288776</v>
+        <v>291336</v>
       </c>
       <c r="AA400" t="inlineStr">
         <is>
-          <t>2026-09-14 07:57:04</t>
+          <t>2026-10-12 07:20:32</t>
         </is>
       </c>
       <c r="AB400" t="inlineStr"/>
@@ -61458,14 +61506,14 @@
       </c>
       <c r="X403" t="inlineStr"/>
       <c r="Y403" t="n">
-        <v>308271</v>
+        <v>312386</v>
       </c>
       <c r="Z403" t="n">
-        <v>201087</v>
+        <v>203771</v>
       </c>
       <c r="AA403" t="inlineStr">
         <is>
-          <t>2026-09-29 10:58:32</t>
+          <t>2026-10-13 08:21:48</t>
         </is>
       </c>
       <c r="AB403" t="inlineStr"/>
@@ -63129,14 +63177,14 @@
       </c>
       <c r="X414" t="inlineStr"/>
       <c r="Y414" t="n">
-        <v>193172</v>
+        <v>197594</v>
       </c>
       <c r="Z414" t="n">
-        <v>126080</v>
+        <v>128785</v>
       </c>
       <c r="AA414" t="inlineStr">
         <is>
-          <t>2026-07-09 09:02:21</t>
+          <t>2026-10-15 10:05:12</t>
         </is>
       </c>
       <c r="AB414" t="inlineStr"/>
@@ -63355,7 +63403,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>BAR BARTH</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -63431,14 +63479,14 @@
       </c>
       <c r="X416" t="inlineStr"/>
       <c r="Y416" t="n">
-        <v>142665</v>
+        <v>154375</v>
       </c>
       <c r="Z416" t="n">
-        <v>92717</v>
+        <v>100580</v>
       </c>
       <c r="AA416" t="inlineStr">
         <is>
-          <t>2025-12-31 09:59:04</t>
+          <t>2026-10-14 08:13:36</t>
         </is>
       </c>
       <c r="AB416" t="inlineStr"/>
@@ -63450,42 +63498,26 @@
       <c r="AD416" t="inlineStr"/>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AF416" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG416" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AF416" t="inlineStr"/>
+      <c r="AG416" t="inlineStr"/>
       <c r="AH416" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI416" t="inlineStr">
-        <is>
-          <t>E038043</t>
-        </is>
-      </c>
-      <c r="AJ416" t="inlineStr">
-        <is>
-          <t>EA560041556A</t>
-        </is>
-      </c>
+      <c r="AI416" t="inlineStr"/>
+      <c r="AJ416" t="inlineStr"/>
       <c r="AK416" t="inlineStr"/>
       <c r="AL416" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AM416" t="inlineStr"/>
       <c r="AN416" t="inlineStr"/>
       <c r="AO416" t="inlineStr"/>
-      <c r="AP416" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
+      <c r="AP416" t="inlineStr"/>
       <c r="AQ416" t="inlineStr"/>
     </row>
     <row r="417">
@@ -63582,14 +63614,14 @@
       </c>
       <c r="X417" t="inlineStr"/>
       <c r="Y417" t="n">
-        <v>157092</v>
+        <v>159316</v>
       </c>
       <c r="Z417" t="n">
-        <v>102386</v>
+        <v>103849</v>
       </c>
       <c r="AA417" t="inlineStr">
         <is>
-          <t>2026-10-02 06:48:08</t>
+          <t>2026-10-15 11:25:00</t>
         </is>
       </c>
       <c r="AB417" t="inlineStr"/>
@@ -63733,14 +63765,14 @@
       </c>
       <c r="X418" t="inlineStr"/>
       <c r="Y418" t="n">
-        <v>479163</v>
+        <v>484418</v>
       </c>
       <c r="Z418" t="n">
-        <v>312294</v>
+        <v>315717</v>
       </c>
       <c r="AA418" t="inlineStr">
         <is>
-          <t>2026-09-23 09:37:02</t>
+          <t>2026-10-12 09:33:40</t>
         </is>
       </c>
       <c r="AB418" t="inlineStr"/>
@@ -64655,14 +64687,14 @@
       </c>
       <c r="X424" t="inlineStr"/>
       <c r="Y424" t="n">
-        <v>38390</v>
+        <v>41728</v>
       </c>
       <c r="Z424" t="n">
-        <v>24498</v>
+        <v>26977</v>
       </c>
       <c r="AA424" t="inlineStr">
         <is>
-          <t>2026-09-29 10:58:02</t>
+          <t>2026-10-13 07:56:19</t>
         </is>
       </c>
       <c r="AB424" t="inlineStr"/>
@@ -65263,14 +65295,14 @@
       </c>
       <c r="X428" t="inlineStr"/>
       <c r="Y428" t="n">
-        <v>104018</v>
+        <v>105749</v>
       </c>
       <c r="Z428" t="n">
-        <v>68049</v>
+        <v>68950</v>
       </c>
       <c r="AA428" t="inlineStr">
         <is>
-          <t>2026-10-01 10:20:30</t>
+          <t>2026-10-15 09:12:55</t>
         </is>
       </c>
       <c r="AB428" t="inlineStr"/>
@@ -66097,7 +66129,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
+          <t>MIMI' CAFE'</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -66192,26 +66224,42 @@
       <c r="AD434" t="inlineStr"/>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="AF434" t="inlineStr"/>
-      <c r="AG434" t="inlineStr"/>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AF434" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG434" t="n">
+        <v>0</v>
+      </c>
       <c r="AH434" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI434" t="inlineStr"/>
-      <c r="AJ434" t="inlineStr"/>
+      <c r="AI434" t="inlineStr">
+        <is>
+          <t>E041082</t>
+        </is>
+      </c>
+      <c r="AJ434" t="inlineStr">
+        <is>
+          <t>EA570010976A</t>
+        </is>
+      </c>
       <c r="AK434" t="inlineStr"/>
       <c r="AL434" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="AM434" t="inlineStr"/>
       <c r="AN434" t="inlineStr"/>
       <c r="AO434" t="inlineStr"/>
-      <c r="AP434" t="inlineStr"/>
+      <c r="AP434" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
       <c r="AQ434" t="inlineStr"/>
     </row>
     <row r="435">
@@ -66962,7 +67010,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO AWP ASSEGNATE</t>
+          <t>BAR BARTH</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -67057,26 +67105,42 @@
       <c r="AD440" t="inlineStr"/>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AF440" t="inlineStr"/>
-      <c r="AG440" t="inlineStr"/>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AF440" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG440" t="n">
+        <v>0</v>
+      </c>
       <c r="AH440" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI440" t="inlineStr"/>
-      <c r="AJ440" t="inlineStr"/>
+      <c r="AI440" t="inlineStr">
+        <is>
+          <t>E038043</t>
+        </is>
+      </c>
+      <c r="AJ440" t="inlineStr">
+        <is>
+          <t>EA560041556A</t>
+        </is>
+      </c>
       <c r="AK440" t="inlineStr"/>
       <c r="AL440" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AM440" t="inlineStr"/>
       <c r="AN440" t="inlineStr"/>
       <c r="AO440" t="inlineStr"/>
-      <c r="AP440" t="inlineStr"/>
+      <c r="AP440" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
       <c r="AQ440" t="inlineStr"/>
     </row>
     <row r="441">
@@ -67475,14 +67539,14 @@
       </c>
       <c r="X443" t="inlineStr"/>
       <c r="Y443" t="n">
-        <v>150390</v>
+        <v>153743</v>
       </c>
       <c r="Z443" t="n">
-        <v>98195</v>
+        <v>100381</v>
       </c>
       <c r="AA443" t="inlineStr">
         <is>
-          <t>2026-07-22 10:12:35</t>
+          <t>2026-10-13 10:20:13</t>
         </is>
       </c>
       <c r="AB443" t="inlineStr"/>
@@ -68925,7 +68989,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>AL CAFFERINO</t>
+          <t>WINGAMING SRL - DEPOSITO GUASTI</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -69020,30 +69084,18 @@
       <c r="AD453" t="inlineStr"/>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AF453" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG453" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AF453" t="inlineStr"/>
+      <c r="AG453" t="inlineStr"/>
       <c r="AH453" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI453" t="inlineStr">
-        <is>
-          <t>E036981</t>
-        </is>
-      </c>
-      <c r="AJ453" t="inlineStr">
-        <is>
-          <t>EA570008867A</t>
-        </is>
-      </c>
+      <c r="AI453" t="inlineStr"/>
+      <c r="AJ453" t="inlineStr"/>
       <c r="AK453" t="inlineStr"/>
       <c r="AL453" t="n">
         <v>0</v>
@@ -69051,11 +69103,7 @@
       <c r="AM453" t="inlineStr"/>
       <c r="AN453" t="inlineStr"/>
       <c r="AO453" t="inlineStr"/>
-      <c r="AP453" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+      <c r="AP453" t="inlineStr"/>
       <c r="AQ453" t="inlineStr"/>
     </row>
     <row r="454">
@@ -69764,14 +69812,14 @@
       </c>
       <c r="X458" t="inlineStr"/>
       <c r="Y458" t="n">
-        <v>321998</v>
+        <v>323243</v>
       </c>
       <c r="Z458" t="n">
-        <v>210702</v>
+        <v>211358</v>
       </c>
       <c r="AA458" t="inlineStr">
         <is>
-          <t>2026-09-14 07:57:19</t>
+          <t>2026-10-12 07:20:58</t>
         </is>
       </c>
       <c r="AB458" t="inlineStr"/>
@@ -70654,14 +70702,14 @@
       </c>
       <c r="X464" t="inlineStr"/>
       <c r="Y464" t="n">
-        <v>318262</v>
+        <v>320256</v>
       </c>
       <c r="Z464" t="n">
-        <v>207756</v>
+        <v>209015</v>
       </c>
       <c r="AA464" t="inlineStr">
         <is>
-          <t>2026-09-29 07:32:02</t>
+          <t>2026-10-13 05:58:33</t>
         </is>
       </c>
       <c r="AB464" t="inlineStr"/>
@@ -71111,14 +71159,14 @@
       </c>
       <c r="X467" t="inlineStr"/>
       <c r="Y467" t="n">
-        <v>405125</v>
+        <v>406324</v>
       </c>
       <c r="Z467" t="n">
-        <v>263185</v>
+        <v>264019</v>
       </c>
       <c r="AA467" t="inlineStr">
         <is>
-          <t>2026-09-29 10:58:12</t>
+          <t>2026-10-13 07:56:47</t>
         </is>
       </c>
       <c r="AB467" t="inlineStr"/>
@@ -71266,14 +71314,14 @@
       </c>
       <c r="X468" t="inlineStr"/>
       <c r="Y468" t="n">
-        <v>304416</v>
+        <v>305773</v>
       </c>
       <c r="Z468" t="n">
-        <v>198225</v>
+        <v>199082</v>
       </c>
       <c r="AA468" t="inlineStr">
         <is>
-          <t>2026-10-07 10:31:58</t>
+          <t>2026-10-14 11:21:34</t>
         </is>
       </c>
       <c r="AB468" t="inlineStr"/>
@@ -72029,14 +72077,14 @@
       </c>
       <c r="X473" t="inlineStr"/>
       <c r="Y473" t="n">
-        <v>504366</v>
+        <v>513432</v>
       </c>
       <c r="Z473" t="n">
-        <v>328477</v>
+        <v>333944</v>
       </c>
       <c r="AA473" t="inlineStr">
         <is>
-          <t>2026-07-11 09:01:58</t>
+          <t>2026-10-15 10:57:51</t>
         </is>
       </c>
       <c r="AB473" t="inlineStr"/>
@@ -72180,14 +72228,14 @@
       </c>
       <c r="X474" t="inlineStr"/>
       <c r="Y474" t="n">
-        <v>217563</v>
+        <v>217866</v>
       </c>
       <c r="Z474" t="n">
-        <v>141162</v>
+        <v>141322</v>
       </c>
       <c r="AA474" t="inlineStr">
         <is>
-          <t>2026-10-06 11:16:37</t>
+          <t>2026-10-13 11:11:11</t>
         </is>
       </c>
       <c r="AB474" t="inlineStr"/>
@@ -73559,14 +73607,14 @@
       </c>
       <c r="X483" t="inlineStr"/>
       <c r="Y483" t="n">
-        <v>250655</v>
+        <v>253600</v>
       </c>
       <c r="Z483" t="n">
-        <v>163181</v>
+        <v>165432</v>
       </c>
       <c r="AA483" t="inlineStr">
         <is>
-          <t>2026-09-30 11:14:24</t>
+          <t>2026-10-15 08:30:49</t>
         </is>
       </c>
       <c r="AB483" t="inlineStr"/>
@@ -73608,7 +73656,7 @@
       </c>
       <c r="AK483" t="inlineStr"/>
       <c r="AL483" t="n">
-        <v>2000</v>
+        <v>2283</v>
       </c>
       <c r="AM483" t="inlineStr"/>
       <c r="AN483" t="inlineStr"/>
@@ -73638,7 +73686,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>MIMI' CAFE'</t>
+          <t>WINGAMING SRL</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -73714,14 +73762,14 @@
       </c>
       <c r="X484" t="inlineStr"/>
       <c r="Y484" t="n">
-        <v>173100</v>
+        <v>175485</v>
       </c>
       <c r="Z484" t="n">
-        <v>112594</v>
+        <v>114012</v>
       </c>
       <c r="AA484" t="inlineStr">
         <is>
-          <t>2026-09-17 13:05:40</t>
+          <t>2026-10-13 07:33:11</t>
         </is>
       </c>
       <c r="AB484" t="inlineStr"/>
@@ -73733,42 +73781,26 @@
       <c r="AD484" t="inlineStr"/>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="AF484" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG484" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AF484" t="inlineStr"/>
+      <c r="AG484" t="inlineStr"/>
       <c r="AH484" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI484" t="inlineStr">
-        <is>
-          <t>E041082</t>
-        </is>
-      </c>
-      <c r="AJ484" t="inlineStr">
-        <is>
-          <t>EA570010976A</t>
-        </is>
-      </c>
+      <c r="AI484" t="inlineStr"/>
+      <c r="AJ484" t="inlineStr"/>
       <c r="AK484" t="inlineStr"/>
       <c r="AL484" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="AM484" t="inlineStr"/>
       <c r="AN484" t="inlineStr"/>
       <c r="AO484" t="inlineStr"/>
-      <c r="AP484" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
+      <c r="AP484" t="inlineStr"/>
       <c r="AQ484" t="inlineStr"/>
     </row>
     <row r="485">
@@ -74624,14 +74656,14 @@
       </c>
       <c r="X490" t="inlineStr"/>
       <c r="Y490" t="n">
-        <v>767189</v>
+        <v>770477</v>
       </c>
       <c r="Z490" t="n">
-        <v>500345</v>
+        <v>502624</v>
       </c>
       <c r="AA490" t="inlineStr">
         <is>
-          <t>2026-10-06 12:27:51</t>
+          <t>2026-10-13 12:32:05</t>
         </is>
       </c>
       <c r="AB490" t="inlineStr"/>
@@ -74775,14 +74807,14 @@
       </c>
       <c r="X491" t="inlineStr"/>
       <c r="Y491" t="n">
-        <v>258661</v>
+        <v>261429</v>
       </c>
       <c r="Z491" t="n">
-        <v>168529</v>
+        <v>170320</v>
       </c>
       <c r="AA491" t="inlineStr">
         <is>
-          <t>2026-09-30 11:14:12</t>
+          <t>2026-10-15 08:31:14</t>
         </is>
       </c>
       <c r="AB491" t="inlineStr"/>
@@ -75836,14 +75868,14 @@
       </c>
       <c r="X498" t="inlineStr"/>
       <c r="Y498" t="n">
-        <v>536902</v>
+        <v>539769</v>
       </c>
       <c r="Z498" t="n">
-        <v>349413</v>
+        <v>352338</v>
       </c>
       <c r="AA498" t="inlineStr">
         <is>
-          <t>2026-10-01 11:42:16</t>
+          <t>2026-10-14 11:22:27</t>
         </is>
       </c>
       <c r="AB498" t="inlineStr"/>
@@ -76277,14 +76309,14 @@
       </c>
       <c r="X501" t="inlineStr"/>
       <c r="Y501" t="n">
-        <v>922092</v>
+        <v>929014</v>
       </c>
       <c r="Z501" t="n">
-        <v>601552</v>
+        <v>605663</v>
       </c>
       <c r="AA501" t="inlineStr">
         <is>
-          <t>2026-10-01 11:20:45</t>
+          <t>2026-10-15 10:53:18</t>
         </is>
       </c>
       <c r="AB501" t="inlineStr"/>
@@ -77020,14 +77052,14 @@
       </c>
       <c r="X506" t="inlineStr"/>
       <c r="Y506" t="n">
-        <v>334761</v>
+        <v>340151</v>
       </c>
       <c r="Z506" t="n">
-        <v>217805</v>
+        <v>221147</v>
       </c>
       <c r="AA506" t="inlineStr">
         <is>
-          <t>2026-09-30 11:13:48</t>
+          <t>2026-10-15 08:30:39</t>
         </is>
       </c>
       <c r="AB506" t="inlineStr"/>
@@ -77479,14 +77511,14 @@
       </c>
       <c r="X509" t="inlineStr"/>
       <c r="Y509" t="n">
-        <v>439709</v>
+        <v>440026</v>
       </c>
       <c r="Z509" t="n">
-        <v>287005</v>
+        <v>287177</v>
       </c>
       <c r="AA509" t="inlineStr">
         <is>
-          <t>2026-10-02 14:47:17</t>
+          <t>2026-10-13 17:25:59</t>
         </is>
       </c>
       <c r="AB509" t="inlineStr"/>
@@ -77630,14 +77662,14 @@
       </c>
       <c r="X510" t="inlineStr"/>
       <c r="Y510" t="n">
-        <v>689398</v>
+        <v>691242</v>
       </c>
       <c r="Z510" t="n">
-        <v>449651</v>
+        <v>450646</v>
       </c>
       <c r="AA510" t="inlineStr">
         <is>
-          <t>2026-10-06 12:30:11</t>
+          <t>2026-10-13 11:36:05</t>
         </is>
       </c>
       <c r="AB510" t="inlineStr"/>
@@ -77928,14 +77960,14 @@
       </c>
       <c r="X512" t="inlineStr"/>
       <c r="Y512" t="n">
-        <v>687469</v>
+        <v>691467</v>
       </c>
       <c r="Z512" t="n">
-        <v>446974</v>
+        <v>449729</v>
       </c>
       <c r="AA512" t="inlineStr">
         <is>
-          <t>2026-10-02 09:39:14</t>
+          <t>2026-10-15 10:02:33</t>
         </is>
       </c>
       <c r="AB512" t="inlineStr"/>
@@ -78238,14 +78270,14 @@
       </c>
       <c r="X514" t="inlineStr"/>
       <c r="Y514" t="n">
-        <v>330771</v>
+        <v>336130</v>
       </c>
       <c r="Z514" t="n">
-        <v>215311</v>
+        <v>218999</v>
       </c>
       <c r="AA514" t="inlineStr">
         <is>
-          <t>2026-09-23 09:36:33</t>
+          <t>2026-10-12 09:33:51</t>
         </is>
       </c>
       <c r="AB514" t="inlineStr"/>
@@ -78544,14 +78576,14 @@
       </c>
       <c r="X516" t="inlineStr"/>
       <c r="Y516" t="n">
-        <v>416390</v>
+        <v>419951</v>
       </c>
       <c r="Z516" t="n">
-        <v>270772</v>
+        <v>272966</v>
       </c>
       <c r="AA516" t="inlineStr">
         <is>
-          <t>2026-10-01 11:47:16</t>
+          <t>2026-10-15 11:36:59</t>
         </is>
       </c>
       <c r="AB516" t="inlineStr"/>
@@ -78699,14 +78731,14 @@
       </c>
       <c r="X517" t="inlineStr"/>
       <c r="Y517" t="n">
-        <v>488356</v>
+        <v>495189</v>
       </c>
       <c r="Z517" t="n">
-        <v>318437</v>
+        <v>323140</v>
       </c>
       <c r="AA517" t="inlineStr">
         <is>
-          <t>2026-10-01 11:22:27</t>
+          <t>2026-10-15 10:49:09</t>
         </is>
       </c>
       <c r="AB517" t="inlineStr"/>
@@ -78895,7 +78927,7 @@
       </c>
       <c r="AK518" t="inlineStr"/>
       <c r="AL518" t="n">
-        <v>1550</v>
+        <v>1200</v>
       </c>
       <c r="AM518" t="inlineStr"/>
       <c r="AN518" t="inlineStr"/>
@@ -79152,14 +79184,14 @@
       </c>
       <c r="X520" t="inlineStr"/>
       <c r="Y520" t="n">
-        <v>768346</v>
+        <v>772439</v>
       </c>
       <c r="Z520" t="n">
-        <v>501338</v>
+        <v>503851</v>
       </c>
       <c r="AA520" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:21</t>
+          <t>2026-10-15 10:02:19</t>
         </is>
       </c>
       <c r="AB520" t="inlineStr"/>
@@ -79613,14 +79645,14 @@
       </c>
       <c r="X523" t="inlineStr"/>
       <c r="Y523" t="n">
-        <v>706502</v>
+        <v>710518</v>
       </c>
       <c r="Z523" t="n">
-        <v>460225</v>
+        <v>463002</v>
       </c>
       <c r="AA523" t="inlineStr">
         <is>
-          <t>2026-09-28 10:35:44</t>
+          <t>2026-10-12 10:06:37</t>
         </is>
       </c>
       <c r="AB523" t="inlineStr"/>
@@ -79764,14 +79796,14 @@
       </c>
       <c r="X524" t="inlineStr"/>
       <c r="Y524" t="n">
-        <v>721304</v>
+        <v>724725</v>
       </c>
       <c r="Z524" t="n">
-        <v>470482</v>
+        <v>472878</v>
       </c>
       <c r="AA524" t="inlineStr">
         <is>
-          <t>2026-10-07 12:44:43</t>
+          <t>2026-10-15 12:29:52</t>
         </is>
       </c>
       <c r="AB524" t="inlineStr"/>
@@ -79839,7 +79871,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>WINGAMING SRL - DEPOSITO GUASTI</t>
+          <t>AL CAFFERINO</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -79934,18 +79966,30 @@
       <c r="AD525" t="inlineStr"/>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AF525" t="inlineStr"/>
-      <c r="AG525" t="inlineStr"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AF525" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG525" t="n">
+        <v>0</v>
+      </c>
       <c r="AH525" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AI525" t="inlineStr"/>
-      <c r="AJ525" t="inlineStr"/>
+      <c r="AI525" t="inlineStr">
+        <is>
+          <t>E036981</t>
+        </is>
+      </c>
+      <c r="AJ525" t="inlineStr">
+        <is>
+          <t>EA570008867A</t>
+        </is>
+      </c>
       <c r="AK525" t="inlineStr"/>
       <c r="AL525" t="n">
         <v>0</v>
@@ -79953,7 +79997,11 @@
       <c r="AM525" t="inlineStr"/>
       <c r="AN525" t="inlineStr"/>
       <c r="AO525" t="inlineStr"/>
-      <c r="AP525" t="inlineStr"/>
+      <c r="AP525" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
       <c r="AQ525" t="inlineStr"/>
     </row>
     <row r="526">
@@ -80638,14 +80686,14 @@
       </c>
       <c r="X530" t="inlineStr"/>
       <c r="Y530" t="n">
-        <v>448907</v>
+        <v>451048</v>
       </c>
       <c r="Z530" t="n">
-        <v>292645</v>
+        <v>294147</v>
       </c>
       <c r="AA530" t="inlineStr">
         <is>
-          <t>2026-10-01 08:58:24</t>
+          <t>2026-10-15 07:55:36</t>
         </is>
       </c>
       <c r="AB530" t="inlineStr"/>
@@ -80789,14 +80837,14 @@
       </c>
       <c r="X531" t="inlineStr"/>
       <c r="Y531" t="n">
-        <v>664375</v>
+        <v>667366</v>
       </c>
       <c r="Z531" t="n">
-        <v>432981</v>
+        <v>434931</v>
       </c>
       <c r="AA531" t="inlineStr">
         <is>
-          <t>2026-10-05 10:17:13</t>
+          <t>2026-10-12 09:45:37</t>
         </is>
       </c>
       <c r="AB531" t="inlineStr"/>
